--- a/src/attributions/attributions_saliency_traj_391.xlsx
+++ b/src/attributions/attributions_saliency_traj_391.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4.783263284480199e-05</v>
+        <v>4.256249212630792e-06</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0003013904206454754</v>
+        <v>1.633460783523333e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>3.337506132083945e-05</v>
+        <v>7.141146625144756e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.803856038255617e-05</v>
+        <v>1.685309143795166e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.665785309043713e-05</v>
+        <v>5.372447731133434e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003216079494450241</v>
+        <v>6.611497155972756e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.256240910966881e-06</v>
+        <v>2.431207576591987e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.55099496623734e-05</v>
+        <v>3.976247171522118e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.930983489728533e-05</v>
+        <v>7.525208616243617e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001189033791888505</v>
+        <v>3.131160156044643e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002241553156636655</v>
+        <v>3.907468453689944e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>2.645874155859929e-05</v>
+        <v>1.286632141273003e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>4.474024171940982e-05</v>
+        <v>9.001195167002152e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.101423888234422e-05</v>
+        <v>1.961152975127334e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002204964403063059</v>
+        <v>6.999378001637524e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.484696051396895e-05</v>
+        <v>3.906617621396435e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.544609641423449e-05</v>
+        <v>3.34621927322587e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>6.612673314521089e-05</v>
+        <v>2.023286015173653e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.751326453813817e-05</v>
+        <v>1.435216177014809e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>3.271242894697934e-05</v>
+        <v>3.657853540062206e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.785259883035906e-05</v>
+        <v>1.810728235795978e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>2.227242475782987e-05</v>
+        <v>2.57222723121231e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>8.67368362378329e-05</v>
+        <v>5.176533250050852e-06</v>
       </c>
       <c r="X4" t="n">
-        <v>2.714062793529592e-05</v>
+        <v>4.396372332848841e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.607743590488099e-05</v>
+        <v>1.076882199413376e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.242097070848104e-05</v>
+        <v>8.295241968880873e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.656432505114935e-05</v>
+        <v>7.456715422904381e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.547438245732337e-05</v>
+        <v>6.172382427394041e-08</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.234367341065081e-06</v>
+        <v>5.649158083542716e-07</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.714380389079452e-05</v>
+        <v>1.123871243180474e-06</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.924331733491272e-05</v>
+        <v>4.189282094557711e-07</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.58032692829147e-05</v>
+        <v>1.001157897917437e-06</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.326479393057525e-05</v>
+        <v>2.326617902781436e-07</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.110848072334193e-05</v>
+        <v>6.153638310024689e-07</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.210052505484782e-05</v>
+        <v>2.945110054497491e-06</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.018106665171217e-06</v>
+        <v>9.77540935309662e-07</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.408783297549235e-06</v>
+        <v>6.026479013598873e-07</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.084752329916228e-05</v>
+        <v>8.059326432885427e-07</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.75229210476391e-05</v>
+        <v>1.152608888332907e-07</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.121751797152683e-05</v>
+        <v>2.180187038902659e-06</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.381984348990954e-06</v>
+        <v>2.747825874394039e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.321325054159388e-05</v>
+        <v>7.158093353609729e-07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.606229776982218e-05</v>
+        <v>2.045641167569556e-07</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.46562264894601e-05</v>
+        <v>1.176204023067839e-06</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.904923404566944e-05</v>
+        <v>4.92902472615242e-07</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.572396286064759e-06</v>
+        <v>1.411518724125926e-07</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.000105309096397832</v>
+        <v>6.90319029672537e-06</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.101454295683652e-05</v>
+        <v>7.552941951871617e-07</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.743091706885025e-05</v>
+        <v>6.918257895449642e-07</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.417679545236751e-05</v>
+        <v>1.212363258673577e-07</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0001206065571750514</v>
+        <v>3.989524884673301e-06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.989822188392282e-05</v>
+        <v>2.160030817321967e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.559520311886445e-05</v>
+        <v>2.803948746077367e-06</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0001298816059716046</v>
+        <v>2.21578375203535e-07</v>
       </c>
       <c r="BC4" t="n">
-        <v>9.191040589939803e-05</v>
+        <v>3.47915306520008e-06</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.865853356430307e-05</v>
+        <v>7.748598136458895e-07</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.210126669728197e-05</v>
+        <v>7.30945941995742e-07</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.22854975820519e-05</v>
+        <v>1.319172497460386e-06</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.723095430061221e-05</v>
+        <v>1.840496906879707e-06</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0001358523586532101</v>
+        <v>6.996432375672157e-07</v>
       </c>
       <c r="BI4" t="n">
-        <v>7.529082358814776e-05</v>
+        <v>8.457145668216981e-07</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3.731324250111356e-05</v>
+        <v>5.277908257994568e-06</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.377833000849932e-05</v>
+        <v>1.039742301145452e-06</v>
       </c>
       <c r="BL4" t="n">
-        <v>3.589336301956791e-06</v>
+        <v>8.631133141534519e-07</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.170458290289389e-05</v>
+        <v>2.379324087087298e-06</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.147060280956794e-06</v>
+        <v>4.323032243291891e-08</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.949706893356051e-05</v>
+        <v>1.327372615378408e-06</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.723486487520859e-05</v>
+        <v>1.014184704217769e-06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.189382601296529e-05</v>
+        <v>7.127337084966712e-07</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.728979572770186e-05</v>
+        <v>1.562439479130262e-06</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.816401532385498e-06</v>
+        <v>1.998005245695822e-06</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.841110446956009e-05</v>
+        <v>9.735841786095989e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.956441519723739e-05</v>
+        <v>1.081376353795349e-06</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.26262733223848e-05</v>
+        <v>1.875163775366673e-07</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.198699000175111e-05</v>
+        <v>2.078053512377664e-06</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.388076270814054e-05</v>
+        <v>4.130654815526213e-06</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.12407345417887e-05</v>
+        <v>4.211702162137954e-06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.029545380035415e-06</v>
+        <v>5.237949153524823e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.305018465965986e-06</v>
+        <v>4.784812404068362e-07</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.096183263551211e-06</v>
+        <v>2.9979526061652e-07</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.426740269991569e-05</v>
+        <v>1.218167653860291e-06</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.958437213848811e-06</v>
+        <v>7.987367212081153e-07</v>
       </c>
       <c r="CE4" t="n">
-        <v>3.779242979362607e-05</v>
+        <v>7.772673598083202e-07</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.604165820230264e-05</v>
+        <v>3.536662802616775e-07</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.175471516035032e-05</v>
+        <v>9.411972996531404e-07</v>
       </c>
       <c r="CH4" t="n">
-        <v>2.465526813466568e-05</v>
+        <v>3.782777753258415e-07</v>
       </c>
       <c r="CI4" t="n">
-        <v>5.457310544443317e-05</v>
+        <v>1.982582261916832e-06</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.886308564280625e-05</v>
+        <v>5.119592287883279e-07</v>
       </c>
       <c r="CK4" t="n">
-        <v>3.141713023069315e-07</v>
+        <v>5.637916729028802e-07</v>
       </c>
       <c r="CL4" t="n">
-        <v>3.463184475549497e-05</v>
+        <v>4.667199391406029e-07</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.970506648125593e-05</v>
+        <v>2.141424602086772e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>6.258926441660151e-05</v>
+        <v>4.051705218444113e-06</v>
       </c>
       <c r="CO4" t="n">
-        <v>5.994903040118515e-05</v>
+        <v>6.047562237654347e-07</v>
       </c>
       <c r="CP4" t="n">
-        <v>3.870198997901753e-05</v>
+        <v>3.383391060651775e-07</v>
       </c>
       <c r="CQ4" t="n">
-        <v>9.740233508637175e-06</v>
+        <v>1.227135726367123e-06</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.561657518323045e-05</v>
+        <v>2.752005912043387e-06</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.656654578458983e-05</v>
+        <v>1.909115326270694e-06</v>
       </c>
       <c r="CT4" t="n">
-        <v>9.894110917230137e-06</v>
+        <v>1.063425088432268e-06</v>
       </c>
       <c r="CU4" t="n">
-        <v>5.754737503593788e-05</v>
+        <v>4.491161575970182e-07</v>
       </c>
       <c r="CV4" t="n">
-        <v>3.912771262548631e-07</v>
+        <v>9.775510534382192e-07</v>
       </c>
       <c r="CW4" t="n">
-        <v>4.920769788441248e-05</v>
+        <v>4.575456955535628e-07</v>
       </c>
       <c r="CX4" t="n">
-        <v>2.128356391040143e-05</v>
+        <v>3.255144065406057e-08</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.701498877082486e-05</v>
+        <v>7.607936822751071e-07</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.140464468742721e-05</v>
+        <v>1.811702645682089e-07</v>
       </c>
       <c r="DA4" t="n">
-        <v>5.314914960763417e-05</v>
+        <v>1.540031121294305e-06</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.000565473281313e-06</v>
+        <v>5.103438525111414e-07</v>
       </c>
       <c r="DC4" t="n">
-        <v>4.372151124698576e-06</v>
+        <v>1.140955419032252e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.80753081117291e-05</v>
+        <v>1.51321117414227e-07</v>
       </c>
       <c r="DE4" t="n">
-        <v>4.076477853232063e-05</v>
+        <v>1.902030362543883e-06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.323569267697167e-05</v>
+        <v>2.071368953693309e-06</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.107984230155125e-05</v>
+        <v>8.610749659965222e-07</v>
       </c>
       <c r="DH4" t="n">
-        <v>8.49352145451121e-05</v>
+        <v>1.374226599182293e-07</v>
       </c>
       <c r="DI4" t="n">
-        <v>4.414016802911647e-05</v>
+        <v>8.249889447142777e-07</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0001634937798371539</v>
+        <v>1.452780793442798e-06</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.181229400681332e-05</v>
+        <v>6.578392230949248e-07</v>
       </c>
       <c r="DL4" t="n">
-        <v>3.616264075390063e-05</v>
+        <v>4.367061023913266e-07</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0001409475516993552</v>
+        <v>8.302381502289791e-07</v>
       </c>
       <c r="DN4" t="n">
-        <v>2.17803826672025e-05</v>
+        <v>8.245646654359007e-08</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.350498951069312e-05</v>
+        <v>2.453289198456332e-07</v>
       </c>
       <c r="DP4" t="n">
-        <v>2.118437623721547e-05</v>
+        <v>1.657100483498652e-06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>2.352312367293052e-05</v>
+        <v>2.420172450001701e-06</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.431368895689957e-05</v>
+        <v>1.751533545757411e-06</v>
       </c>
       <c r="DS4" t="n">
-        <v>1.3158248293621e-05</v>
+        <v>2.076537157336134e-06</v>
       </c>
       <c r="DT4" t="n">
-        <v>5.172490637050942e-05</v>
+        <v>1.597455138835358e-06</v>
       </c>
       <c r="DU4" t="n">
-        <v>1.473525662731845e-05</v>
+        <v>1.055900611390825e-06</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.485318327671848e-05</v>
+        <v>5.85981183576223e-07</v>
       </c>
       <c r="DW4" t="n">
-        <v>2.234165913250763e-05</v>
+        <v>1.352754111394461e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.319253301015124e-05</v>
+        <v>8.618768561063916e-07</v>
       </c>
       <c r="DY4" t="n">
-        <v>1.594076638866682e-05</v>
+        <v>1.376640057060285e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.988412208855152e-05</v>
+        <v>4.103089281670691e-07</v>
       </c>
       <c r="EA4" t="n">
-        <v>1.953401078935713e-05</v>
+        <v>1.246245574293425e-06</v>
       </c>
       <c r="EB4" t="n">
-        <v>8.893726771930233e-06</v>
+        <v>7.537613555541611e-07</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.290338125021663e-05</v>
+        <v>5.376750777941197e-07</v>
       </c>
       <c r="ED4" t="n">
-        <v>2.934088479378261e-05</v>
+        <v>1.399591383233201e-06</v>
       </c>
       <c r="EE4" t="n">
-        <v>3.874692629324272e-05</v>
+        <v>1.749198077050096e-06</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.71335123013705e-05</v>
+        <v>1.315375243393646e-06</v>
       </c>
       <c r="EG4" t="n">
-        <v>4.413039641804062e-05</v>
+        <v>1.215547626998159e-06</v>
       </c>
       <c r="EH4" t="n">
-        <v>1.054679796652636e-05</v>
+        <v>1.102136252484343e-06</v>
       </c>
       <c r="EI4" t="n">
-        <v>5.46220107935369e-05</v>
+        <v>1.033202238431841e-06</v>
       </c>
       <c r="EJ4" t="n">
-        <v>3.956961154472083e-05</v>
+        <v>1.534654302304261e-06</v>
       </c>
       <c r="EK4" t="n">
-        <v>2.036838668573182e-05</v>
+        <v>1.903708380268654e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>3.768701208173297e-05</v>
+        <v>1.346247699984815e-07</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.712098537609563e-06</v>
+        <v>1.970889940139386e-08</v>
       </c>
       <c r="EN4" t="n">
-        <v>6.265314368647523e-06</v>
+        <v>7.174978122748144e-07</v>
       </c>
       <c r="EO4" t="n">
-        <v>2.278438296343666e-05</v>
+        <v>6.084363803893211e-07</v>
       </c>
       <c r="EP4" t="n">
-        <v>9.031200534082018e-06</v>
+        <v>2.703784502955386e-07</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.07637642940972e-05</v>
+        <v>2.159990344807738e-06</v>
       </c>
       <c r="ER4" t="n">
-        <v>2.272506571898703e-05</v>
+        <v>6.810149102420837e-07</v>
       </c>
       <c r="ES4" t="n">
-        <v>8.468591840937734e-05</v>
+        <v>8.702691616235825e-07</v>
       </c>
       <c r="ET4" t="n">
-        <v>9.761824912857264e-05</v>
+        <v>3.049922952413908e-06</v>
       </c>
       <c r="EU4" t="n">
-        <v>3.987116360804066e-05</v>
+        <v>8.822959216558957e-07</v>
       </c>
       <c r="EV4" t="n">
-        <v>3.009875581483357e-05</v>
+        <v>7.189765938164783e-07</v>
       </c>
       <c r="EW4" t="n">
-        <v>6.883895548526198e-05</v>
+        <v>7.265443002779648e-08</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.055741336131177e-06</v>
+        <v>1.21887228488049e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>5.012193651054986e-05</v>
+        <v>8.407063774029666e-07</v>
       </c>
       <c r="EZ4" t="n">
-        <v>7.794744306011125e-06</v>
+        <v>1.329033523234102e-07</v>
       </c>
       <c r="FA4" t="n">
-        <v>7.195412763394415e-07</v>
+        <v>1.034428692037181e-06</v>
       </c>
       <c r="FB4" t="n">
-        <v>3.712218676810153e-05</v>
+        <v>1.673709562055592e-07</v>
       </c>
       <c r="FC4" t="n">
-        <v>4.071461444254965e-05</v>
+        <v>2.029652250712388e-06</v>
       </c>
       <c r="FD4" t="n">
-        <v>2.742684773693327e-05</v>
+        <v>4.650225662317098e-07</v>
       </c>
       <c r="FE4" t="n">
-        <v>1.081804475688841e-05</v>
+        <v>4.159142008575145e-07</v>
       </c>
       <c r="FF4" t="n">
-        <v>5.367449921322986e-05</v>
+        <v>9.806838363601855e-08</v>
       </c>
       <c r="FG4" t="n">
-        <v>2.968246189993806e-05</v>
+        <v>1.998709649342345e-06</v>
       </c>
       <c r="FH4" t="n">
-        <v>2.343119740544353e-05</v>
+        <v>1.365997377433814e-07</v>
       </c>
       <c r="FI4" t="n">
-        <v>2.407890315225814e-05</v>
+        <v>5.489397949531849e-07</v>
       </c>
       <c r="FJ4" t="n">
-        <v>6.735137139912695e-05</v>
+        <v>6.616409109483357e-08</v>
       </c>
       <c r="FK4" t="n">
-        <v>2.420019154669717e-05</v>
+        <v>2.47599041358626e-06</v>
       </c>
       <c r="FL4" t="n">
-        <v>6.273262260947376e-05</v>
+        <v>1.506280682406214e-06</v>
       </c>
       <c r="FM4" t="n">
-        <v>1.473131123930216e-05</v>
+        <v>3.284301897110709e-08</v>
       </c>
       <c r="FN4" t="n">
-        <v>2.611989839351736e-05</v>
+        <v>7.812114404259773e-07</v>
       </c>
       <c r="FO4" t="n">
-        <v>3.579492477001622e-05</v>
+        <v>1.181052425636153e-06</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.782404069672339e-05</v>
+        <v>2.857234221664839e-06</v>
       </c>
       <c r="FQ4" t="n">
-        <v>7.02094694133848e-05</v>
+        <v>1.82414419214183e-06</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.369572004885413e-05</v>
+        <v>1.04869411643449e-06</v>
       </c>
       <c r="FS4" t="n">
-        <v>2.411187961115502e-05</v>
+        <v>5.521004595721024e-07</v>
       </c>
       <c r="FT4" t="n">
-        <v>5.679839887307025e-05</v>
+        <v>6.995738203841029e-06</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0001056386536220089</v>
+        <v>1.50883465721563e-06</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.075474185403436e-05</v>
+        <v>2.867059265554417e-06</v>
       </c>
       <c r="FW4" t="n">
-        <v>3.315735375508666e-05</v>
+        <v>1.771088477653393e-06</v>
       </c>
       <c r="FX4" t="n">
-        <v>3.552248381311074e-05</v>
+        <v>1.524052663626208e-06</v>
       </c>
       <c r="FY4" t="n">
-        <v>5.399086148827337e-05</v>
+        <v>1.533522322461067e-07</v>
       </c>
       <c r="FZ4" t="n">
-        <v>2.85000915027922e-05</v>
+        <v>2.352750925638247e-06</v>
       </c>
       <c r="GA4" t="n">
-        <v>1.313822281190369e-06</v>
+        <v>1.79740186467825e-06</v>
       </c>
       <c r="GB4" t="n">
-        <v>4.056000761920586e-05</v>
+        <v>5.432569878394133e-07</v>
       </c>
       <c r="GC4" t="n">
-        <v>7.514865137636662e-05</v>
+        <v>1.980724846362136e-06</v>
       </c>
       <c r="GD4" t="n">
-        <v>3.902548087353352e-06</v>
+        <v>1.627002802706556e-06</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.850879561970942e-05</v>
+        <v>7.22269874131598e-07</v>
       </c>
       <c r="GF4" t="n">
-        <v>2.17070228245575e-05</v>
+        <v>1.251839080396167e-06</v>
       </c>
       <c r="GG4" t="n">
-        <v>3.383791045052931e-05</v>
+        <v>3.037139038042369e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0009007810149341822</v>
+        <v>0.003179058432579041</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01470008585602045</v>
+        <v>0.04848895221948624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002069704467430711</v>
+        <v>0.007807613350450993</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008650004863739014</v>
+        <v>0.03589490056037903</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009849358350038528</v>
+        <v>0.002784216077998281</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00311117572709918</v>
+        <v>0.008320009335875511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001983196008950472</v>
+        <v>0.02608683705329895</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001446641981601715</v>
+        <v>0.01700068265199661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006927022477611899</v>
+        <v>0.009484278038144112</v>
       </c>
       <c r="J5" t="n">
-        <v>8.027395233511925e-05</v>
+        <v>0.008256320841610432</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01125502586364746</v>
+        <v>0.04628459364175797</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001124465954490006</v>
+        <v>0.01538359373807907</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008549354039132595</v>
+        <v>0.04768967628479004</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01353269349783659</v>
+        <v>0.01266129966825247</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004274997860193253</v>
+        <v>0.01180994510650635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002195632550865412</v>
+        <v>0.0246199294924736</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0005382809322327375</v>
+        <v>0.004762913100421429</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0016158806392923</v>
+        <v>0.006848392076790333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0004880429769400507</v>
+        <v>0.001722700661048293</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002981214551255107</v>
+        <v>0.007047447375953197</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001981705892831087</v>
+        <v>0.001555019058287144</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006533947307616472</v>
+        <v>0.0004683269653469324</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001395495957694948</v>
+        <v>0.005006396677345037</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002820124616846442</v>
+        <v>0.009603505022823811</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002141237491741776</v>
+        <v>0.003457689192146063</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001983990892767906</v>
+        <v>0.01681585982441902</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003809787740465254</v>
+        <v>0.00420008972287178</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002978332806378603</v>
+        <v>0.0001298874849453568</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001569935237057507</v>
+        <v>0.003736001905053854</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001869030063971877</v>
+        <v>0.006210977211594582</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001553225214593112</v>
+        <v>0.004250249825417995</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003333067055791616</v>
+        <v>0.001315647270530462</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0008228570222854614</v>
+        <v>0.0232493095099926</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.469191819429398e-06</v>
+        <v>0.002919208956882358</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0005325538222678006</v>
+        <v>0.01164068095386028</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002425298793241382</v>
+        <v>0.00185344135388732</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0004544680123217404</v>
+        <v>0.002373315859586</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0006263306131586432</v>
+        <v>0.0128971291705966</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0005383002571761608</v>
+        <v>0.007263578474521637</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0004946771077811718</v>
+        <v>0.004076942801475525</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.004708372987806797</v>
+        <v>0.008178458549082279</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.00308259017765522</v>
+        <v>0.007470919284969568</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0001760607701726258</v>
+        <v>0.006694761104881763</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0001686079776845872</v>
+        <v>1.361101021757349e-05</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0002440353273414075</v>
+        <v>0.0004753427929244936</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0008214347180910408</v>
+        <v>0.001272068242542446</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01037997286766768</v>
+        <v>0.01686305180191994</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0003060526796616614</v>
+        <v>0.006612238939851522</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001317886053584516</v>
+        <v>0.01682486571371555</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001973162870854139</v>
+        <v>0.03279630839824677</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001395543455146253</v>
+        <v>0.01230192370712757</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0009384443983435631</v>
+        <v>0.0008417757926508784</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.001086775097064674</v>
+        <v>0.0006172930588945746</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.004567433148622513</v>
+        <v>0.005001720506697893</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.001745308749377728</v>
+        <v>0.008297815918922424</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.005232703872025013</v>
+        <v>0.004305734299123287</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003936220426112413</v>
+        <v>0.0089148273691535</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.003013695357367396</v>
+        <v>0.003300178097561002</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.00865531899034977</v>
+        <v>0.0163873303681612</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.006345944944769144</v>
+        <v>0.003577994182705879</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.002976445015519857</v>
+        <v>0.008483684621751308</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0006967965746298432</v>
+        <v>0.02199575677514076</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.002762299263849854</v>
+        <v>0.002782835625112057</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.002352879149839282</v>
+        <v>0.0006995972944423556</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.004606841132044792</v>
+        <v>0.008910126984119415</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.002251408295705914</v>
+        <v>0.004828643519431353</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001639579189941287</v>
+        <v>0.007398464251309633</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.005511459894478321</v>
+        <v>0.009947381913661957</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.003820175770670176</v>
+        <v>0.00196854630485177</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0009224466630257666</v>
+        <v>0.002565998584032059</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.002013663295656443</v>
+        <v>0.004532897844910622</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001804908271878958</v>
+        <v>0.007005561608821154</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.000802439171820879</v>
+        <v>0.001462397631257772</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.004181783646345139</v>
+        <v>0.01597854681313038</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.00165310618467629</v>
+        <v>0.007175816688686609</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0008479709504172206</v>
+        <v>0.02315538376569748</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001391685334965587</v>
+        <v>0.0001822373596951365</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.002644429448992014</v>
+        <v>0.008213014341890812</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0004020835040137172</v>
+        <v>0.00490869814530015</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.001269559375941753</v>
+        <v>0.003332604421302676</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001696776365861297</v>
+        <v>0.0004135783528909087</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001715835533104837</v>
+        <v>0.001304411212913692</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.00248416792601347</v>
+        <v>0.01358070224523544</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.000361586338840425</v>
+        <v>0.0008924733847379684</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0009162100614048541</v>
+        <v>0.01481631584465504</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0006764373974874616</v>
+        <v>0.002701792633160949</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0005304520018398762</v>
+        <v>0.0004526195698417723</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0006207788246683776</v>
+        <v>0.0009279950754716992</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0002913218340836465</v>
+        <v>0.0001876747701317072</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001518339151516557</v>
+        <v>0.002155717462301254</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.003446074202656746</v>
+        <v>0.004176114220172167</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.002978118136525154</v>
+        <v>0.0002454160712659359</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0003153849102091044</v>
+        <v>0.01961217075586319</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.002932007191702724</v>
+        <v>0.0276012122631073</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.003893605200573802</v>
+        <v>0.002931535243988037</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0003688517026603222</v>
+        <v>0.00911580678075552</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0001709436764940619</v>
+        <v>0.01395270973443985</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.002985089784488082</v>
+        <v>0.009498806670308113</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001094103790819645</v>
+        <v>0.003964788280427456</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.332930696662515e-05</v>
+        <v>0.001293721725232899</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001729618757963181</v>
+        <v>0.01346109248697758</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.00102032907307148</v>
+        <v>0.002188070910051465</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001032370375469327</v>
+        <v>0.0155600793659687</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.000637228018604219</v>
+        <v>0.0002752639993559569</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001161027539637871</v>
+        <v>0.001273641362786293</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0003715311468113214</v>
+        <v>0.0003546830266714096</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0004002772620879114</v>
+        <v>0.0005451714969240129</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.000723477394785732</v>
+        <v>0.0003063828335143626</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.002463998040184379</v>
+        <v>0.002843254478648305</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.003657924709841609</v>
+        <v>0.01373083516955376</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.00365153537131846</v>
+        <v>0.002712072804570198</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.00611812062561512</v>
+        <v>0.01835378259420395</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.002229071455076337</v>
+        <v>0.007099897600710392</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001599354087375104</v>
+        <v>0.01950427517294884</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0001223614235641435</v>
+        <v>0.003684872295707464</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.002167371334508061</v>
+        <v>0.0225384496152401</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0005149170756340027</v>
+        <v>0.001002808567136526</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.000913401716388762</v>
+        <v>0.001661458052694798</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.001358648063614964</v>
+        <v>0.006607718765735626</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001379560213536024</v>
+        <v>0.0001481566578149796</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0003223490784876049</v>
+        <v>0.009994486346840858</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0008622559253126383</v>
+        <v>0.001794503885321319</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0002375000040046871</v>
+        <v>0.002968110144138336</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001766669447533786</v>
+        <v>0.009057211689651012</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0009056612616404891</v>
+        <v>0.004286791197955608</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.002765995915979147</v>
+        <v>0.02109992504119873</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0008421476231887937</v>
+        <v>8.826545672491193e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.001750281313434243</v>
+        <v>0.004217731766402721</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0008198491996154189</v>
+        <v>0.007540710270404816</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0008081539417617023</v>
+        <v>0.0009260945953428745</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001292648143135011</v>
+        <v>0.004605178255587816</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.003848082851618528</v>
+        <v>0.006442048586905003</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0008952261996455491</v>
+        <v>0.003033301327377558</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001004228834062815</v>
+        <v>0.02334333583712578</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0006303080590441823</v>
+        <v>0.01649749279022217</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0005673182313330472</v>
+        <v>0.007511808071285486</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001859434531070292</v>
+        <v>0.01037588436156511</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.000207370292628184</v>
+        <v>0.006441302597522736</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.00203683041036129</v>
+        <v>0.01714212819933891</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.003047154750674963</v>
+        <v>0.004540550522506237</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0003053740656469017</v>
+        <v>0.003255432238802314</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001948703546077013</v>
+        <v>0.001452174969017506</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0003858442651107907</v>
+        <v>0.004007373470813036</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.00104134320281446</v>
+        <v>0.001281082280911505</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001349687343463302</v>
+        <v>0.001525220926851034</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.002053637988865376</v>
+        <v>0.01792133972048759</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0004723909078165889</v>
+        <v>0.002618307480588555</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001690963108558208</v>
+        <v>0.008555260486900806</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.001099471235647798</v>
+        <v>0.002443368546664715</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001403457019478083</v>
+        <v>0.006248334422707558</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0005950310733169317</v>
+        <v>0.006139408797025681</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.001500114100053906</v>
+        <v>0.001978123560547829</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001325045945122838</v>
+        <v>0.006801245268434286</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0007635201909579337</v>
+        <v>0.0009882920421659946</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.002118631731718779</v>
+        <v>0.0134559478610754</v>
       </c>
       <c r="EZ5" t="n">
-        <v>8.812844316707924e-05</v>
+        <v>0.001596310641616583</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001078611705452204</v>
+        <v>0.01909782364964485</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.001517763826996088</v>
+        <v>0.0008571065845899284</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.00106108165346086</v>
+        <v>0.001020011259242892</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001929823192767799</v>
+        <v>0.00100172299426049</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0003446317568887025</v>
+        <v>0.0002767953556030989</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0004733547102659941</v>
+        <v>0.001663584262132645</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.000704795413184911</v>
+        <v>0.005491637624800205</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.002034848323091865</v>
+        <v>0.006743828766047955</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001144673093222082</v>
+        <v>0.003851223737001419</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.002063495339825749</v>
+        <v>0.01197786629199982</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001523434184491634</v>
+        <v>0.00504382187500596</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.002523576142266393</v>
+        <v>0.003984203096479177</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.000820942223072052</v>
+        <v>0.00151149439625442</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0007007318781688809</v>
+        <v>0.005852498114109039</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0001551180030219257</v>
+        <v>0.002502443501725793</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001483755884692073</v>
+        <v>0.009602521546185017</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0002119400160154328</v>
+        <v>0.01678794994950294</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.00104222958907485</v>
+        <v>0.0004449919797480106</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001335764187388122</v>
+        <v>0.007915633730590343</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.004274301696568727</v>
+        <v>0.01629995182156563</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001979234395548701</v>
+        <v>0.01584077998995781</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0002081764978356659</v>
+        <v>0.005639242008328438</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002946480643004179</v>
+        <v>0.005145934410393238</v>
       </c>
       <c r="FX5" t="n">
-        <v>9.610271081328392e-05</v>
+        <v>0.01873476430773735</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002069700043648481</v>
+        <v>0.004403899889439344</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001482149236835539</v>
+        <v>0.002316292840987444</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001964528812095523</v>
+        <v>0.004726354032754898</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001004108693450689</v>
+        <v>0.01790955662727356</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.003177136415615678</v>
+        <v>0.0008457187796011567</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.002272561891004443</v>
+        <v>0.004675804637372494</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0004042161162942648</v>
+        <v>0.009098915383219719</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.002636933699250221</v>
+        <v>0.0007196820224635303</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002345209009945393</v>
+        <v>0.00213695946149528</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0005293999565765262</v>
+        <v>1.374684871144338e-13</v>
       </c>
       <c r="B6" t="n">
-        <v>0.000398086936911568</v>
+        <v>2.611435373500726e-13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001731958182062954</v>
+        <v>6.592186377937098e-14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004634725337382406</v>
+        <v>1.369668030523023e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001605380792170763</v>
+        <v>1.473312709896271e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001245042076334357</v>
+        <v>4.108146928107764e-13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006591996643692255</v>
+        <v>3.018711040685129e-13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0004074975149706006</v>
+        <v>7.036907406603177e-13</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00129890046082437</v>
+        <v>2.358570356706356e-14</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0007029160624369979</v>
+        <v>1.350298318254436e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0007418290479108691</v>
+        <v>1.793452945831817e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001016066380543634</v>
+        <v>1.607463348627519e-13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001834926515584812</v>
+        <v>1.057551873222089e-13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001767693087458611</v>
+        <v>2.937241921040223e-13</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000965864397585392</v>
+        <v>4.812886200689093e-13</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001914761960506439</v>
+        <v>5.506429188485706e-13</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.179219831712544e-05</v>
+        <v>6.646531740782391e-13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000356469361577183</v>
+        <v>4.360430067148688e-14</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003240795049350709</v>
+        <v>2.398417158237451e-14</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0003888136416207999</v>
+        <v>1.771198340988836e-13</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000124496640637517</v>
+        <v>1.007309199160117e-14</v>
       </c>
       <c r="V6" t="n">
-        <v>5.160628279554658e-05</v>
+        <v>9.176435110912207e-14</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0006179744959808886</v>
+        <v>3.179853028025675e-13</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004434675793163478</v>
+        <v>2.92529807885758e-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0003125718503724784</v>
+        <v>1.313024531766557e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001055962347891182</v>
+        <v>4.268170831957935e-13</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0005863952683284879</v>
+        <v>4.325485977019596e-15</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.377670848043635e-07</v>
+        <v>1.063260536473404e-13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0007372626569122076</v>
+        <v>1.737843538778677e-13</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0005034292116761208</v>
+        <v>8.696954831646786e-15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0003445998299866915</v>
+        <v>5.847428932118787e-14</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001464566215872765</v>
+        <v>1.328686509774468e-13</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001276039867661893</v>
+        <v>2.57303130624803e-13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0009715516353026032</v>
+        <v>1.204935673806973e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0004812878032680601</v>
+        <v>1.421652238205867e-13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0008103792788460851</v>
+        <v>1.224380704245229e-14</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0002111538924509659</v>
+        <v>7.717120670790167e-14</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0003692401805892587</v>
+        <v>7.540811779258721e-14</v>
       </c>
       <c r="AM6" t="n">
-        <v>9.454902465222403e-05</v>
+        <v>1.717522269697146e-14</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0008157185511663556</v>
+        <v>7.984249112552577e-14</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0005343618104234338</v>
+        <v>1.159043835300549e-13</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001632998755667359</v>
+        <v>4.984046216103405e-14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0005918409442529082</v>
+        <v>8.363307876096959e-14</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0004339795559644699</v>
+        <v>8.788446587224691e-14</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0001862973149400204</v>
+        <v>9.552384924726987e-14</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0002289886469952762</v>
+        <v>2.149979684302333e-15</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.000298178696539253</v>
+        <v>4.083243346306858e-13</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.00032394117442891</v>
+        <v>1.831294447682263e-13</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0004494090680964291</v>
+        <v>1.546070671661071e-13</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001145584508776665</v>
+        <v>2.274707386427238e-13</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0006595330778509378</v>
+        <v>4.416239238452108e-13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001694071106612682</v>
+        <v>6.761316495833974e-14</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0007440962363034487</v>
+        <v>2.160828617816038e-13</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.000514619518071413</v>
+        <v>3.380280471222512e-14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0007036030292510986</v>
+        <v>1.357841654869504e-13</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0006429825443774462</v>
+        <v>3.678322024140007e-13</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36501039378345e-05</v>
+        <v>4.057307468512475e-14</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.531687591224909e-05</v>
+        <v>2.068689186965345e-13</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001525216037407517</v>
+        <v>1.32891419223069e-13</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.00118052086327225</v>
+        <v>1.797651925320581e-13</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0004618936509359628</v>
+        <v>8.794940958237879e-14</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0004906263784505427</v>
+        <v>6.124203791660343e-13</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0008074201177805662</v>
+        <v>7.221823237080899e-14</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0001324747281614691</v>
+        <v>1.009706031350303e-13</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0006270219455473125</v>
+        <v>1.033021121443246e-13</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0003901207237504423</v>
+        <v>3.822270733429278e-14</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.000847859017085284</v>
+        <v>4.795890382958481e-14</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0001217899844050407</v>
+        <v>1.501652263907055e-13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0003139699692837894</v>
+        <v>6.982009913801546e-14</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0008199093863368034</v>
+        <v>5.580289309521473e-14</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.686939013889059e-05</v>
+        <v>2.532989348325888e-14</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0005851269816048443</v>
+        <v>8.878622392415741e-14</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0001427643001079559</v>
+        <v>2.714339102333034e-14</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0001001892378553748</v>
+        <v>3.245529726588793e-14</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0003410639183130115</v>
+        <v>5.570976351673002e-15</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0003175312594976276</v>
+        <v>2.494474895739507e-13</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0006483718752861023</v>
+        <v>2.17080463305562e-13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.308400871697813e-05</v>
+        <v>1.118338684462025e-13</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0004055015160702169</v>
+        <v>8.194854029305171e-15</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0003747314331121743</v>
+        <v>1.173426996846014e-13</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0003742468834389001</v>
+        <v>5.168398871315157e-14</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.300691580283456e-05</v>
+        <v>5.633066916025352e-14</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.00011648017243715</v>
+        <v>4.530462783354158e-14</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0001812341943150386</v>
+        <v>1.443387849021406e-14</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0002993194793816656</v>
+        <v>3.187751576377504e-14</v>
       </c>
       <c r="CH6" t="n">
-        <v>3.665780241135508e-05</v>
+        <v>6.445297312356046e-15</v>
       </c>
       <c r="CI6" t="n">
-        <v>3.72734029951971e-05</v>
+        <v>9.377045716513557e-14</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0002113741356879473</v>
+        <v>3.78597571045261e-14</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0001548451837152243</v>
+        <v>4.388336075815749e-14</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0003192401200067252</v>
+        <v>1.13191953639985e-13</v>
       </c>
       <c r="CM6" t="n">
-        <v>7.410580292344093e-05</v>
+        <v>1.306522706863433e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0003671599843073636</v>
+        <v>1.85579687467935e-13</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0002032947959378362</v>
+        <v>1.14156622522954e-13</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0007228553877212107</v>
+        <v>7.684082320089103e-14</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0007921906653791666</v>
+        <v>5.29231064354263e-14</v>
       </c>
       <c r="CR6" t="n">
-        <v>5.698059248970821e-05</v>
+        <v>9.051437442446353e-14</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0003876141854561865</v>
+        <v>3.637516991176343e-13</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0002820142544806004</v>
+        <v>1.645079878527175e-13</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.001583496225066483</v>
+        <v>2.015571005454034e-13</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.253852678928524e-05</v>
+        <v>3.852140164468075e-14</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0001671565696597099</v>
+        <v>2.1753049529857e-14</v>
       </c>
       <c r="CX6" t="n">
-        <v>2.792099257931113e-05</v>
+        <v>2.193956279671061e-14</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0002642968902364373</v>
+        <v>3.48057560962782e-14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0001106971394619904</v>
+        <v>8.47220310942233e-14</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0001511088339611888</v>
+        <v>1.240225641369747e-13</v>
       </c>
       <c r="DB6" t="n">
-        <v>4.542234819382429e-05</v>
+        <v>7.886303643542952e-14</v>
       </c>
       <c r="DC6" t="n">
-        <v>8.858388173393905e-05</v>
+        <v>3.509188043772891e-14</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0002692528651095927</v>
+        <v>1.077153367586361e-13</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0003235990589018911</v>
+        <v>2.508499050840607e-13</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0008022315450944006</v>
+        <v>3.371529130099388e-13</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0001572357723489404</v>
+        <v>1.600488133950834e-13</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0008247144287452102</v>
+        <v>1.604400613015519e-13</v>
       </c>
       <c r="DI6" t="n">
-        <v>1.11766712507233e-05</v>
+        <v>8.005989398989985e-14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.001653499552048743</v>
+        <v>4.544908015473997e-13</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0007203507702797651</v>
+        <v>7.728121934709106e-14</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0002522511640563607</v>
+        <v>1.662132345821299e-13</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.001282910350710154</v>
+        <v>2.735054478904264e-14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0002409092849120498</v>
+        <v>2.281242686072438e-13</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001486122782807797</v>
+        <v>2.432738594447016e-14</v>
       </c>
       <c r="DP6" t="n">
-        <v>7.303715392481536e-05</v>
+        <v>1.510733405778522e-14</v>
       </c>
       <c r="DQ6" t="n">
-        <v>5.442084511741996e-05</v>
+        <v>4.010065933826579e-13</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001160636893473566</v>
+        <v>2.326355796368473e-13</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.000654912437312305</v>
+        <v>1.154094994484239e-13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.001002896227873862</v>
+        <v>1.867832874046654e-13</v>
       </c>
       <c r="DU6" t="n">
-        <v>3.914582703146152e-05</v>
+        <v>8.834679000738546e-14</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.001221415586769581</v>
+        <v>3.295609702562256e-14</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.000315928045893088</v>
+        <v>6.404231799820442e-14</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0002254386054119095</v>
+        <v>9.651729014539118e-14</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0001312085369136184</v>
+        <v>1.599425480296526e-13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.000648590677883476</v>
+        <v>1.574739958657562e-13</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.000491645245347172</v>
+        <v>2.121447277830119e-13</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0001777610887074843</v>
+        <v>2.051093669908077e-13</v>
       </c>
       <c r="EC6" t="n">
-        <v>4.85284035676159e-05</v>
+        <v>1.079791909098377e-13</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.000477244146168232</v>
+        <v>8.491259317856478e-14</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0001507937122369185</v>
+        <v>2.267553278392093e-14</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0001613052154425532</v>
+        <v>3.360718414712263e-15</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0002478705137036741</v>
+        <v>2.622453984654424e-14</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0001094253893825226</v>
+        <v>1.159843298877486e-13</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.001389714423567057</v>
+        <v>1.823408774231233e-13</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0002502040879335254</v>
+        <v>1.483503939267092e-13</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.00106725946534425</v>
+        <v>9.884240913813139e-14</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0007820866303518414</v>
+        <v>2.579196350851326e-14</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0002402255777269602</v>
+        <v>8.864528441799788e-15</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0002318871847819537</v>
+        <v>1.587818147363168e-13</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0003084428899455816</v>
+        <v>8.211139423562261e-14</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0001787241490092129</v>
+        <v>1.723133083702394e-13</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0002049374452326447</v>
+        <v>1.226138467017371e-14</v>
       </c>
       <c r="ER6" t="n">
-        <v>7.543539686594158e-05</v>
+        <v>7.123061228310121e-14</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0001772303803591058</v>
+        <v>1.592719283283889e-13</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.000578399864025414</v>
+        <v>1.695663737460301e-14</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0005957223474979401</v>
+        <v>4.846164837696634e-14</v>
       </c>
       <c r="EV6" t="n">
-        <v>7.524570537498221e-05</v>
+        <v>1.676644120849474e-14</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0003141557681374252</v>
+        <v>2.150401167896887e-14</v>
       </c>
       <c r="EX6" t="n">
-        <v>3.621992073021829e-05</v>
+        <v>5.607046402698879e-14</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0001247169566340744</v>
+        <v>2.295723561338697e-14</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001808291999623179</v>
+        <v>9.734046725671901e-15</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0004398262244649231</v>
+        <v>2.868345955176453e-14</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0001006373131531291</v>
+        <v>7.144877408899603e-14</v>
       </c>
       <c r="FC6" t="n">
-        <v>7.209382602013648e-08</v>
+        <v>1.140788852271868e-13</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0001784641208359972</v>
+        <v>5.429977214393977e-14</v>
       </c>
       <c r="FE6" t="n">
-        <v>9.292978938901797e-05</v>
+        <v>5.108653571787164e-14</v>
       </c>
       <c r="FF6" t="n">
-        <v>7.535023905802518e-05</v>
+        <v>9.601220101081165e-14</v>
       </c>
       <c r="FG6" t="n">
-        <v>6.754083733540028e-05</v>
+        <v>2.738784134377614e-13</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0002410751767456532</v>
+        <v>4.733567053952226e-14</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0002782277588266879</v>
+        <v>9.439949093682093e-14</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0008697997545823455</v>
+        <v>7.364842378532535e-14</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0004861041088588536</v>
+        <v>2.692968630480398e-14</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.000439841765910387</v>
+        <v>9.632141547040451e-14</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0003395529929548502</v>
+        <v>4.353550804364267e-14</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0002449314924888313</v>
+        <v>2.691971266125665e-13</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0006966203218325973</v>
+        <v>1.490626469913964e-13</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0005343629163689911</v>
+        <v>9.177211670718249e-14</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0002244195202365518</v>
+        <v>3.740865310662006e-13</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0006024481263011694</v>
+        <v>3.297262907587389e-13</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0001151774922618642</v>
+        <v>3.155507064954606e-14</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001005558064207435</v>
+        <v>1.288711433573841e-13</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.001562131219543517</v>
+        <v>4.805074930612149e-14</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0004155562492087483</v>
+        <v>4.137040373903417e-13</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0005597424460574985</v>
+        <v>2.328101090815632e-13</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0002159449795726687</v>
+        <v>1.173599927092525e-13</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0002838139189407229</v>
+        <v>3.719319977327738e-14</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.000397080642869696</v>
+        <v>2.961639180426578e-14</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0004025679081678391</v>
+        <v>9.107684495902185e-14</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0003910134546458721</v>
+        <v>2.922555047361192e-15</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0006113670533522964</v>
+        <v>2.631254860264304e-13</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0003220264334231615</v>
+        <v>1.380697991918214e-13</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.001177636673673987</v>
+        <v>2.979678525807548e-15</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.000742347096092999</v>
+        <v>2.168126924740124e-13</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.001630572718568146</v>
+        <v>4.594661782118814e-14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.060442622602409e-09</v>
+        <v>4.615351835051899e-18</v>
       </c>
       <c r="B7" t="n">
-        <v>1.400553006902783e-09</v>
+        <v>2.0636796398271e-17</v>
       </c>
       <c r="C7" t="n">
-        <v>2.693759215688374e-09</v>
+        <v>1.507158479401834e-17</v>
       </c>
       <c r="D7" t="n">
-        <v>7.660875822601554e-10</v>
+        <v>2.641237823026938e-17</v>
       </c>
       <c r="E7" t="n">
-        <v>3.640997059406459e-09</v>
+        <v>3.453705374024485e-17</v>
       </c>
       <c r="F7" t="n">
-        <v>2.880035099295242e-09</v>
+        <v>8.411215175503024e-17</v>
       </c>
       <c r="G7" t="n">
-        <v>5.291937554829929e-09</v>
+        <v>1.056805950597748e-20</v>
       </c>
       <c r="H7" t="n">
-        <v>1.012847361536728e-09</v>
+        <v>1.838459865724837e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>8.013933960882014e-10</v>
+        <v>1.018921078542819e-16</v>
       </c>
       <c r="J7" t="n">
-        <v>4.014468757418399e-10</v>
+        <v>4.144913541177679e-18</v>
       </c>
       <c r="K7" t="n">
-        <v>2.79440026673683e-09</v>
+        <v>9.10952104862029e-17</v>
       </c>
       <c r="L7" t="n">
-        <v>3.251479974153426e-09</v>
+        <v>8.047854419307057e-18</v>
       </c>
       <c r="M7" t="n">
-        <v>2.871891835454221e-09</v>
+        <v>5.309943667218802e-17</v>
       </c>
       <c r="N7" t="n">
-        <v>1.226356260985995e-08</v>
+        <v>3.624156858025122e-17</v>
       </c>
       <c r="O7" t="n">
-        <v>4.052413959954038e-10</v>
+        <v>9.041440775484725e-17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7724862688695e-09</v>
+        <v>2.192393906224027e-17</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.683790161801426e-09</v>
+        <v>4.27460867834497e-17</v>
       </c>
       <c r="R7" t="n">
-        <v>3.690610039797093e-09</v>
+        <v>7.453387010025411e-17</v>
       </c>
       <c r="S7" t="n">
-        <v>5.87206727686862e-10</v>
+        <v>2.851961918638699e-17</v>
       </c>
       <c r="T7" t="n">
-        <v>9.381434518118681e-10</v>
+        <v>4.926933897316129e-17</v>
       </c>
       <c r="U7" t="n">
-        <v>6.980935829403734e-10</v>
+        <v>2.245727865143486e-17</v>
       </c>
       <c r="V7" t="n">
-        <v>7.76798070312168e-10</v>
+        <v>6.77793712984972e-17</v>
       </c>
       <c r="W7" t="n">
-        <v>1.846529373850103e-09</v>
+        <v>1.033490839328982e-16</v>
       </c>
       <c r="X7" t="n">
-        <v>4.261303310215681e-09</v>
+        <v>4.412685967531507e-17</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.069101778801041e-09</v>
+        <v>1.484900372607012e-17</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.479607880661149e-09</v>
+        <v>2.666523907172072e-17</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.689587524391413e-10</v>
+        <v>2.568400930496949e-17</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.773881207536078e-10</v>
+        <v>3.149402832022967e-17</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.627012106794837e-10</v>
+        <v>1.081411099662628e-17</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.752112315818067e-09</v>
+        <v>2.926960730417657e-17</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.158518057157835e-09</v>
+        <v>6.160564593098112e-17</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.556083789073682e-09</v>
+        <v>3.665200071094901e-19</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.056277065814015e-09</v>
+        <v>2.649424429549375e-17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.382343350897486e-09</v>
+        <v>1.948991709641113e-17</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.003295751507039e-09</v>
+        <v>6.0875166040758e-17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.219298522732061e-09</v>
+        <v>1.652027748598043e-17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.420633943816085e-09</v>
+        <v>3.22861066963084e-17</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.904950529598494e-10</v>
+        <v>2.099943899625915e-17</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.249691792386102e-10</v>
+        <v>1.317738916774743e-17</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.167435592641652e-09</v>
+        <v>6.21902376309295e-17</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.936373005331006e-09</v>
+        <v>3.251401480740146e-17</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.586435094402816e-09</v>
+        <v>9.934581431827221e-18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.008677030789329e-09</v>
+        <v>1.719225420020014e-18</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.52450618795541e-09</v>
+        <v>1.718377725328269e-17</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.514978780787658e-10</v>
+        <v>1.683921682348495e-17</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.29639685045413e-09</v>
+        <v>2.080855548938396e-17</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.29577928784397e-09</v>
+        <v>1.22635799148752e-16</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.609211180448767e-10</v>
+        <v>2.34893800258581e-17</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.140470188929157e-10</v>
+        <v>3.166548962632211e-17</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.526357397897755e-10</v>
+        <v>2.15492560232558e-17</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.382586293871782e-09</v>
+        <v>3.178788506001975e-18</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.28716748371005e-09</v>
+        <v>1.586112372561653e-17</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.088571011109707e-09</v>
+        <v>3.437976038368422e-17</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.274181814560961e-09</v>
+        <v>3.519264400652988e-17</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.056935206023013e-09</v>
+        <v>4.70827358275335e-18</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.488392187276588e-09</v>
+        <v>3.035789574888809e-17</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.790549708502454e-09</v>
+        <v>1.928989489812846e-17</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.834874888284048e-10</v>
+        <v>3.87496066672916e-17</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.991489639863175e-09</v>
+        <v>2.139117022766834e-17</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.12995279799577e-10</v>
+        <v>5.33378036549462e-17</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.497361289461764e-10</v>
+        <v>2.995468490493789e-17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.041120523126438e-10</v>
+        <v>4.826859601575993e-17</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.702892881207731e-09</v>
+        <v>2.650304549721132e-17</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.45858305936153e-10</v>
+        <v>3.98601462704808e-17</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.242054624763568e-09</v>
+        <v>3.959154749069503e-17</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.605276272493739e-10</v>
+        <v>1.929997657543425e-17</v>
       </c>
       <c r="BO7" t="n">
-        <v>8.164906528662641e-10</v>
+        <v>1.14859106941949e-17</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.012566652747182e-08</v>
+        <v>4.571062930694585e-17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.655935832900468e-09</v>
+        <v>3.577996871122213e-17</v>
       </c>
       <c r="BR7" t="n">
-        <v>3.006680016071073e-09</v>
+        <v>6.83347006570959e-17</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.906684836214481e-09</v>
+        <v>8.153711203837306e-18</v>
       </c>
       <c r="BT7" t="n">
-        <v>2.586472147569907e-10</v>
+        <v>9.452522904707856e-18</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.108033553798293e-09</v>
+        <v>2.125810664561061e-17</v>
       </c>
       <c r="BV7" t="n">
-        <v>2.137630072951424e-09</v>
+        <v>1.979164942281332e-17</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.788114597673257e-10</v>
+        <v>3.504746057413702e-17</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.223349532786244e-09</v>
+        <v>7.3232860580496e-17</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.952678907457539e-09</v>
+        <v>6.388599097388771e-17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>9.270986200959896e-10</v>
+        <v>5.160991599955153e-17</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.973204266647599e-09</v>
+        <v>8.896658360252834e-18</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.699487465842367e-10</v>
+        <v>4.582314903131021e-17</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.165810863985485e-09</v>
+        <v>6.277821084522199e-17</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.423314046794971e-11</v>
+        <v>1.976422011370107e-17</v>
       </c>
       <c r="CE7" t="n">
-        <v>6.205811420301188e-10</v>
+        <v>5.774461002268368e-18</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.957008609667412e-10</v>
+        <v>3.938076615418488e-18</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.861330061776357e-10</v>
+        <v>1.584453213688994e-17</v>
       </c>
       <c r="CH7" t="n">
-        <v>4.647640605703884e-10</v>
+        <v>2.145864707254705e-18</v>
       </c>
       <c r="CI7" t="n">
-        <v>3.506422097121487e-10</v>
+        <v>1.489832354291298e-17</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.211537870027257e-09</v>
+        <v>1.190878527566671e-17</v>
       </c>
       <c r="CK7" t="n">
-        <v>7.393596845872707e-10</v>
+        <v>9.486447235989881e-18</v>
       </c>
       <c r="CL7" t="n">
-        <v>7.9075329617595e-10</v>
+        <v>2.716929646723093e-17</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.583455671612001e-09</v>
+        <v>1.886697399454235e-17</v>
       </c>
       <c r="CN7" t="n">
-        <v>3.77017439490146e-09</v>
+        <v>5.651298606706775e-17</v>
       </c>
       <c r="CO7" t="n">
-        <v>6.662002616231177e-10</v>
+        <v>3.824542767623134e-18</v>
       </c>
       <c r="CP7" t="n">
-        <v>8.490956826534557e-10</v>
+        <v>1.341032819132604e-17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>6.764079074628171e-09</v>
+        <v>4.268185124580129e-17</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.593100096286548e-10</v>
+        <v>2.515805809300622e-17</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.947476846453355e-09</v>
+        <v>1.875385373705327e-17</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.816525235260769e-09</v>
+        <v>1.572517328322099e-17</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.6254688706141e-09</v>
+        <v>3.298167956468179e-17</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.294886225495674e-10</v>
+        <v>2.339002239940068e-17</v>
       </c>
       <c r="CW7" t="n">
-        <v>5.266163616290953e-10</v>
+        <v>8.430508997854701e-18</v>
       </c>
       <c r="CX7" t="n">
-        <v>3.742949006291241e-10</v>
+        <v>3.074488061794245e-18</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.295021395148922e-10</v>
+        <v>1.945154584215602e-17</v>
       </c>
       <c r="CZ7" t="n">
-        <v>6.22308982123343e-10</v>
+        <v>2.019454345658891e-18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.312526476393572e-10</v>
+        <v>1.752268307641302e-17</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.380550007645809e-09</v>
+        <v>6.490095482038007e-18</v>
       </c>
       <c r="DC7" t="n">
-        <v>6.974442134932701e-10</v>
+        <v>3.532342870600002e-18</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.558363993403589e-10</v>
+        <v>2.378684410029952e-17</v>
       </c>
       <c r="DE7" t="n">
-        <v>4.385741991796976e-09</v>
+        <v>1.058176258000504e-17</v>
       </c>
       <c r="DF7" t="n">
-        <v>4.311946355528562e-09</v>
+        <v>3.403171586914641e-17</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.327650211990772e-09</v>
+        <v>4.221645296339935e-17</v>
       </c>
       <c r="DH7" t="n">
-        <v>4.180723767177597e-09</v>
+        <v>1.6270546695967e-17</v>
       </c>
       <c r="DI7" t="n">
-        <v>6.496661875132759e-09</v>
+        <v>2.275454751125171e-18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.289108541082442e-09</v>
+        <v>5.288657001335362e-17</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.159268567922481e-09</v>
+        <v>1.373492213549797e-17</v>
       </c>
       <c r="DL7" t="n">
-        <v>4.536806930133253e-09</v>
+        <v>2.931323942712752e-17</v>
       </c>
       <c r="DM7" t="n">
-        <v>1.265645033221574e-09</v>
+        <v>1.196486315811413e-17</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.053327203237586e-09</v>
+        <v>2.323819836105025e-17</v>
       </c>
       <c r="DO7" t="n">
-        <v>6.196104740396891e-11</v>
+        <v>4.670141797285574e-18</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.469854793434422e-09</v>
+        <v>1.613745498976844e-17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.339156341373382e-09</v>
+        <v>6.673232607912758e-17</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.104506569011733e-09</v>
+        <v>3.316297108517381e-17</v>
       </c>
       <c r="DS7" t="n">
-        <v>3.388561098383036e-10</v>
+        <v>3.943246411528883e-17</v>
       </c>
       <c r="DT7" t="n">
-        <v>3.3603453353237e-09</v>
+        <v>3.19562502290794e-17</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.123103692852624e-09</v>
+        <v>1.456468520592339e-17</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.854205565811952e-10</v>
+        <v>7.964168556735068e-18</v>
       </c>
       <c r="DW7" t="n">
-        <v>3.409978965862592e-10</v>
+        <v>2.627790678680909e-17</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.688034600988431e-09</v>
+        <v>7.470009204434664e-18</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.378003904901504e-10</v>
+        <v>1.954725063902841e-17</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.034725277155758e-09</v>
+        <v>2.560326820537819e-17</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.003327865234382e-09</v>
+        <v>1.303049512584781e-17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.22619869813434e-09</v>
+        <v>2.829926488864777e-17</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.354634182604286e-09</v>
+        <v>3.461992400273286e-17</v>
       </c>
       <c r="ED7" t="n">
-        <v>3.392681247049723e-09</v>
+        <v>1.203967668143587e-17</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.142361316652796e-09</v>
+        <v>9.72657942217525e-18</v>
       </c>
       <c r="EF7" t="n">
-        <v>8.831658182550939e-10</v>
+        <v>1.838009383163241e-17</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.540974319842348e-09</v>
+        <v>1.594630678509724e-17</v>
       </c>
       <c r="EH7" t="n">
-        <v>9.554682600665387e-10</v>
+        <v>5.653641968023107e-19</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.697566836573628e-09</v>
+        <v>3.294607440239506e-17</v>
       </c>
       <c r="EJ7" t="n">
-        <v>5.208695696978793e-10</v>
+        <v>1.330622668405563e-17</v>
       </c>
       <c r="EK7" t="n">
-        <v>8.112034932672429e-10</v>
+        <v>8.910071921065994e-18</v>
       </c>
       <c r="EL7" t="n">
-        <v>3.072651577618046e-10</v>
+        <v>1.000728068150328e-17</v>
       </c>
       <c r="EM7" t="n">
-        <v>2.437149648759629e-10</v>
+        <v>1.787872477311299e-17</v>
       </c>
       <c r="EN7" t="n">
-        <v>6.21960927205123e-10</v>
+        <v>3.189603148048554e-17</v>
       </c>
       <c r="EO7" t="n">
-        <v>7.903261378672255e-10</v>
+        <v>4.429291204738203e-18</v>
       </c>
       <c r="EP7" t="n">
-        <v>1.282200456920179e-09</v>
+        <v>2.730021765150215e-17</v>
       </c>
       <c r="EQ7" t="n">
-        <v>3.484618704696629e-10</v>
+        <v>2.699919008298185e-17</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.496888029668298e-09</v>
+        <v>5.807567251924578e-18</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.454850684368125e-09</v>
+        <v>1.132736002310318e-17</v>
       </c>
       <c r="ET7" t="n">
-        <v>4.237885042890355e-10</v>
+        <v>3.620197971613443e-17</v>
       </c>
       <c r="EU7" t="n">
-        <v>3.25131560563463e-10</v>
+        <v>3.142264925081125e-17</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.000171501175373e-09</v>
+        <v>2.59516617901345e-17</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.505370605947576e-09</v>
+        <v>2.282898053149169e-17</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.182175191072332e-10</v>
+        <v>2.868289140441516e-17</v>
       </c>
       <c r="EY7" t="n">
-        <v>3.638931378446841e-10</v>
+        <v>1.1616257815121e-17</v>
       </c>
       <c r="EZ7" t="n">
-        <v>7.265591461802501e-10</v>
+        <v>2.739147800694328e-18</v>
       </c>
       <c r="FA7" t="n">
-        <v>8.463779677114758e-11</v>
+        <v>1.294149214629833e-17</v>
       </c>
       <c r="FB7" t="n">
-        <v>6.381731809668167e-10</v>
+        <v>1.172453865243634e-18</v>
       </c>
       <c r="FC7" t="n">
-        <v>8.675186680129343e-10</v>
+        <v>1.6138730502273e-17</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.462833743026692e-09</v>
+        <v>1.705420768213239e-17</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.193428800227991e-09</v>
+        <v>7.884980075153529e-18</v>
       </c>
       <c r="FF7" t="n">
-        <v>2.233663809469988e-10</v>
+        <v>2.905701196058309e-17</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.216870937348347e-09</v>
+        <v>5.280913929057376e-17</v>
       </c>
       <c r="FH7" t="n">
-        <v>9.704447245795222e-10</v>
+        <v>2.34324402212124e-17</v>
       </c>
       <c r="FI7" t="n">
-        <v>8.873503043460573e-10</v>
+        <v>2.184937700182474e-17</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.555378714712674e-09</v>
+        <v>2.220703335508042e-17</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.294145457464424e-09</v>
+        <v>1.386065607014787e-17</v>
       </c>
       <c r="FL7" t="n">
-        <v>7.234182142212831e-10</v>
+        <v>5.356568198753721e-17</v>
       </c>
       <c r="FM7" t="n">
-        <v>5.580293449547469e-10</v>
+        <v>4.741404565109875e-17</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.334217625270639e-09</v>
+        <v>3.042527870876727e-18</v>
       </c>
       <c r="FO7" t="n">
-        <v>1.721050857383943e-09</v>
+        <v>2.371799785791673e-17</v>
       </c>
       <c r="FP7" t="n">
-        <v>3.129879133645375e-10</v>
+        <v>2.754451221052988e-17</v>
       </c>
       <c r="FQ7" t="n">
-        <v>3.283668448261778e-09</v>
+        <v>6.591274891076514e-17</v>
       </c>
       <c r="FR7" t="n">
-        <v>8.585734345700757e-10</v>
+        <v>2.832812025713607e-17</v>
       </c>
       <c r="FS7" t="n">
-        <v>7.840799121083819e-10</v>
+        <v>4.951792990829062e-17</v>
       </c>
       <c r="FT7" t="n">
-        <v>7.376140254145014e-10</v>
+        <v>3.284884759319558e-18</v>
       </c>
       <c r="FU7" t="n">
-        <v>3.85464682395309e-09</v>
+        <v>4.267435947099339e-18</v>
       </c>
       <c r="FV7" t="n">
-        <v>8.238868476340144e-10</v>
+        <v>4.742161600806484e-17</v>
       </c>
       <c r="FW7" t="n">
-        <v>8.201481715985892e-10</v>
+        <v>3.948221737477267e-17</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.268576355073492e-09</v>
+        <v>3.844870152150196e-17</v>
       </c>
       <c r="FY7" t="n">
-        <v>3.879468413181542e-10</v>
+        <v>2.218851443552658e-17</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.982811026479681e-09</v>
+        <v>2.363482153860207e-17</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.911365732354398e-09</v>
+        <v>8.885157241015897e-18</v>
       </c>
       <c r="GB7" t="n">
-        <v>9.705687364913729e-10</v>
+        <v>6.441035399907487e-18</v>
       </c>
       <c r="GC7" t="n">
-        <v>5.122643642607727e-09</v>
+        <v>1.674439214678432e-17</v>
       </c>
       <c r="GD7" t="n">
-        <v>2.660160980383353e-09</v>
+        <v>4.940255475645173e-17</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.823797446398601e-09</v>
+        <v>1.71643782135571e-18</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.2360042706282e-09</v>
+        <v>2.44327381554442e-17</v>
       </c>
       <c r="GG7" t="n">
-        <v>9.748399865117108e-10</v>
+        <v>2.200406473945583e-17</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.001291609834879637</v>
+        <v>0.002503925934433937</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02222754433751106</v>
+        <v>0.004240924492478371</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001958622597157955</v>
+        <v>0.001109573990106583</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01335079874843359</v>
+        <v>0.00909271277487278</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008039191365242004</v>
+        <v>0.0004535960615612566</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002572095720097423</v>
+        <v>0.005507774651050568</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002720803255215287</v>
+        <v>0.006095257587730885</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002710671396926045</v>
+        <v>0.004464519675821066</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001185135450214148</v>
+        <v>0.0003792644420173019</v>
       </c>
       <c r="J9" t="n">
-        <v>5.658692680299282e-05</v>
+        <v>0.002033994998782873</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01770141161978245</v>
+        <v>0.002501274924725294</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002542002126574516</v>
+        <v>0.0009064699988812208</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01187936961650848</v>
+        <v>0.01372500415891409</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01015020348131657</v>
+        <v>0.002872278215363622</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002124871825799346</v>
+        <v>0.007590724155306816</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001653512008488178</v>
+        <v>0.007141332607716322</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0003403935406822711</v>
+        <v>0.0004557946813292801</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002109882421791553</v>
+        <v>0.001249315799213946</v>
       </c>
       <c r="S9" t="n">
-        <v>0.001386018935590982</v>
+        <v>0.00112456688657403</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004847269970923662</v>
+        <v>0.0001006877282634377</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001815781812183559</v>
+        <v>0.001996806357055902</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0009668317507021129</v>
+        <v>0.000158937182277441</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002340723294764757</v>
+        <v>0.002401460194960237</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003064674325287342</v>
+        <v>0.003525286912918091</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003092522267252207</v>
+        <v>0.0002927066525444388</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001595029258169234</v>
+        <v>0.001844696351327002</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0007170773460529745</v>
+        <v>0.001211610273458064</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001614120323210955</v>
+        <v>0.001444095629267395</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00464560417458415</v>
+        <v>0.001718369079753757</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.59391376352869e-05</v>
+        <v>0.001454315846785903</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001020978670567274</v>
+        <v>0.0006003733142279088</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001690839766524732</v>
+        <v>0.0004324984038248658</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001959262881428003</v>
+        <v>0.003752760821953416</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.899432390928268e-06</v>
+        <v>0.0003185556270182133</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0001172457996290177</v>
+        <v>0.002116754418238997</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0009110345272347331</v>
+        <v>0.002624114044010639</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001600477029569447</v>
+        <v>0.001234715920872986</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001149432850070298</v>
+        <v>0.002318436279892921</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.996381929027848e-05</v>
+        <v>0.002703575883060694</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0001472714066039771</v>
+        <v>0.002492823172360659</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.005273333750665188</v>
+        <v>0.0003108498349320143</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.004258884117007256</v>
+        <v>0.002392879454419017</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0009510594536550343</v>
+        <v>0.002493999665603042</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0006530788377858698</v>
+        <v>0.0008281347691081464</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0007323192548938096</v>
+        <v>0.0007041755598038435</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001613088417798281</v>
+        <v>0.0003287606523372233</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01568963751196861</v>
+        <v>0.001608608290553093</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0014376116450876</v>
+        <v>0.002912512281909585</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.004330016206949949</v>
+        <v>0.004810679238289595</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001674445578828454</v>
+        <v>0.009386850520968437</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.003600752679631114</v>
+        <v>0.005274791270494461</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.002063748193904757</v>
+        <v>0.0005234455456957221</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002777087036520243</v>
+        <v>6.445960025303066e-05</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.001836850424297154</v>
+        <v>0.0007227039313875139</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.00268371868878603</v>
+        <v>0.002497807377949357</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.004985250998288393</v>
+        <v>0.001285231090150774</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003775322809815407</v>
+        <v>0.0001935570035129786</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002140195807442069</v>
+        <v>0.002275956328958273</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.005762489512562752</v>
+        <v>0.006133283954113722</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003870573360472918</v>
+        <v>0.001517401658929884</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.003762937150895596</v>
+        <v>0.002272837795317173</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0001686578034423292</v>
+        <v>0.003865041537210345</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.002303913701325655</v>
+        <v>0.001528540393337607</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001811211812309921</v>
+        <v>0.0006681676604785025</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.007372317835688591</v>
+        <v>0.0004537892527878284</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.003716952633112669</v>
+        <v>0.0009364891448058188</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.002305514644831419</v>
+        <v>0.002457512076944113</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.004615163430571556</v>
+        <v>0.0007352678803727031</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.00294358073733747</v>
+        <v>0.0008510665502399206</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0009068868821486831</v>
+        <v>3.570481203496456e-05</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.000279638625215739</v>
+        <v>0.001046209479682148</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0008665589848533273</v>
+        <v>0.001245504477992654</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001831729314289987</v>
+        <v>0.0001211382914334536</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00877719558775425</v>
+        <v>0.001411393517628312</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.003995736129581928</v>
+        <v>0.002243513474240899</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002958848141133785</v>
+        <v>0.007025505416095257</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.155885734595358e-05</v>
+        <v>0.002830363111570477</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002742526819929481</v>
+        <v>0.003650868311524391</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.000286890339339152</v>
+        <v>0.000346552871633321</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002842925488948822</v>
+        <v>0.0001455174060538411</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0002042460255324841</v>
+        <v>0.001551594119518995</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.613781543914229e-05</v>
+        <v>0.0005447978619486094</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.003780789440497756</v>
+        <v>0.00131686870008707</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.00100606691557914</v>
+        <v>0.0007599273230880499</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001132886973209679</v>
+        <v>0.00387051235884428</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001170010946225375</v>
+        <v>0.0001582800759933889</v>
       </c>
       <c r="CI9" t="n">
-        <v>3.529898094711825e-05</v>
+        <v>0.0003409926139283925</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0006613582372665405</v>
+        <v>0.0005385053809732199</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0007158326916396618</v>
+        <v>0.001122050685808063</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0003173639415763319</v>
+        <v>0.000103127138572745</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.005523236002773046</v>
+        <v>0.0001830708933994174</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.003753365948796272</v>
+        <v>0.0002698485623113811</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0003555869916453958</v>
+        <v>0.00482178945094347</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.004368127323687077</v>
+        <v>0.006629590876400471</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.005399603396654129</v>
+        <v>0.0007452678983099759</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.00107301480602473</v>
+        <v>0.001553576905280352</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.00258774752728641</v>
+        <v>0.001286710845306516</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.005458136554807425</v>
+        <v>0.002448229817673564</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0004760399460792542</v>
+        <v>0.001591162290424109</v>
       </c>
       <c r="CV9" t="n">
-        <v>8.705561776878312e-05</v>
+        <v>0.0003838369739241898</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.003170597599819303</v>
+        <v>0.001032752334140241</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002133123576641083</v>
+        <v>0.0001468392729293555</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.001856339629739523</v>
+        <v>0.00412495294585824</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.161847805837169e-05</v>
+        <v>0.00083758938126266</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001733489480102435</v>
+        <v>0.000408606807468459</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0005313582369126379</v>
+        <v>0.0008262131013907492</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0008504829020239413</v>
+        <v>0.0009080764139071107</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.281102595385164e-05</v>
+        <v>0.0003347638412378728</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001753603923134506</v>
+        <v>4.216135130263865e-05</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.006382538471370935</v>
+        <v>0.0002633158583194017</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001582650351338089</v>
+        <v>0.001593721681274474</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.005771972239017487</v>
+        <v>0.001750182942487299</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001975973602384329</v>
+        <v>0.001343457493931055</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.000345446722349152</v>
+        <v>0.002860859967768192</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002443328034132719</v>
+        <v>6.775038491468877e-05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0004559031222015619</v>
+        <v>0.007479822728782892</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001067456556484103</v>
+        <v>0.002900103572756052</v>
       </c>
       <c r="DN9" t="n">
-        <v>5.779857747256756e-05</v>
+        <v>4.141021054238081e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.002236701548099518</v>
+        <v>0.001302187447436154</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.002421336248517036</v>
+        <v>0.0004555509658530354</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.001105477102100849</v>
+        <v>0.001416532322764397</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0009560909820720553</v>
+        <v>0.0003493408439680934</v>
       </c>
       <c r="DS9" t="n">
-        <v>6.939220475032926e-05</v>
+        <v>0.0007133190520107746</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001584430923685431</v>
+        <v>0.001251820474863052</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0001706351176835597</v>
+        <v>0.002514611463993788</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0008011175086721778</v>
+        <v>0.004913582466542721</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0009898177813738585</v>
+        <v>0.0005552046932280064</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.003371830796822906</v>
+        <v>0.0006239813519641757</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0003309403255116194</v>
+        <v>0.002353968098759651</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004731296794489026</v>
+        <v>0.002222785959020257</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.00208283425308764</v>
+        <v>3.057250432902947e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001796030555851758</v>
+        <v>0.001980340573936701</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001434589619748294</v>
+        <v>0.001262471312656999</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0006018639542162418</v>
+        <v>0.005091785918921232</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0004331461386755109</v>
+        <v>0.00487990491092205</v>
       </c>
       <c r="EF9" t="n">
-        <v>7.187185110524297e-05</v>
+        <v>0.002083107130602002</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.00129722198471427</v>
+        <v>0.000333233387209475</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.001443798188120127</v>
+        <v>0.00239617726765573</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.00273737171664834</v>
+        <v>0.003989932127296925</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.002160071628168225</v>
+        <v>0.0005560985300689936</v>
       </c>
       <c r="EK9" t="n">
-        <v>8.844454714562744e-05</v>
+        <v>2.144882455468178e-05</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0006825875025242567</v>
+        <v>0.0003072690742556006</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0004732718807645142</v>
+        <v>0.0002290613774675876</v>
       </c>
       <c r="EN9" t="n">
-        <v>6.964392377994955e-05</v>
+        <v>0.0008019959786906838</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.000675581453833729</v>
+        <v>0.0009256590274162591</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.003017583629116416</v>
+        <v>0.002442971570417285</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.002017868449911475</v>
+        <v>0.0002143107121810317</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0006507295183837414</v>
+        <v>0.003218051511794329</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0005029067979194224</v>
+        <v>0.000907040317542851</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0003315011272206903</v>
+        <v>0.001087086624465883</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002018734579905868</v>
+        <v>0.001796941156499088</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0006579480832442641</v>
+        <v>0.001260541612282395</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.000961631303653121</v>
+        <v>0.003921620547771454</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0007852036505937576</v>
+        <v>0.000456417357781902</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.003312960499897599</v>
+        <v>0.001251272042281926</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.001089439960196614</v>
+        <v>0.0005570068024098873</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001599370967596769</v>
+        <v>0.004650686401873827</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0002890478644985706</v>
+        <v>9.230540308635682e-05</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0008249699603766203</v>
+        <v>0.0005272087291814387</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0007291404181160033</v>
+        <v>0.001225361018441617</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0009642126387916505</v>
+        <v>0.001313980435952544</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0005319870542734861</v>
+        <v>0.0003423314483370632</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0002429968444630504</v>
+        <v>0.0003136972663924098</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.002245986834168434</v>
+        <v>0.0005341807845979929</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0008603374008089304</v>
+        <v>0.0008723473292775452</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.002220087917521596</v>
+        <v>0.00129638786893338</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.001092287129722536</v>
+        <v>0.0009882174199447036</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.001784227788448334</v>
+        <v>0.0006497013964690268</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.001615257817320526</v>
+        <v>2.743327058851719e-05</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.867092214524746e-05</v>
+        <v>0.0006742943078279495</v>
       </c>
       <c r="FO9" t="n">
-        <v>4.682139842770994e-05</v>
+        <v>0.002037906553596258</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.002250771503895521</v>
+        <v>0.002948586596176028</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.002708060666918755</v>
+        <v>0.00438937172293663</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0003804072039201856</v>
+        <v>0.003974562510848045</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.001057911780662835</v>
+        <v>0.004394426476210356</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.006131683476269245</v>
+        <v>0.004596856888383627</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.002158486982807517</v>
+        <v>0.002674750052392483</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0001403755159117281</v>
+        <v>0.0001846140949055552</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.000482500356156379</v>
+        <v>0.007868903689086437</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001145534624811262</v>
+        <v>0.0001207106033689342</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.003292895620688796</v>
+        <v>5.630531813949347e-05</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0007673079962842166</v>
+        <v>0.002118424046784639</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0004213448264636099</v>
+        <v>0.001354275736957788</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0005963124567642808</v>
+        <v>0.004265172407031059</v>
       </c>
       <c r="GC9" t="n">
-        <v>5.856025381945074e-06</v>
+        <v>0.000506736570969224</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.003371971659362316</v>
+        <v>0.002437613438814878</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.003990497905761003</v>
+        <v>0.003086637705564499</v>
       </c>
       <c r="GF9" t="n">
-        <v>4.930788418278098e-05</v>
+        <v>0.000673395988997072</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.001666521653532982</v>
+        <v>0.0005682064220309258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.03696444258093834</v>
+        <v>0.0109304441139102</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2427522391080856</v>
+        <v>0.02953724935650826</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02614753507077694</v>
+        <v>0.003814444877207279</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06696204841136932</v>
+        <v>0.07228291779756546</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002411645837128162</v>
+        <v>0.01392816193401814</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03530226275324821</v>
+        <v>0.0184892863035202</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01926810294389725</v>
+        <v>0.0435105562210083</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00881834514439106</v>
+        <v>0.04304863885045052</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002905456814914942</v>
+        <v>0.02564730122685432</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04063446819782257</v>
+        <v>0.0175164733082056</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1513701677322388</v>
+        <v>0.01733304001390934</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003651106264442205</v>
+        <v>0.004473339766263962</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09838427603244781</v>
+        <v>0.09867699444293976</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04488104954361916</v>
+        <v>0.04694444686174393</v>
       </c>
       <c r="O10" t="n">
-        <v>0.066056028008461</v>
+        <v>0.006563438568264246</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01703839935362339</v>
+        <v>0.04178339615464211</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.009131854400038719</v>
+        <v>0.0118476003408432</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003745334688574076</v>
+        <v>0.02346785925328732</v>
       </c>
       <c r="S10" t="n">
-        <v>0.008463470265269279</v>
+        <v>0.002078948309645057</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04042564705014229</v>
+        <v>0.01023937296122313</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02250915393233299</v>
+        <v>0.0004619075916707516</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02401679940521717</v>
+        <v>0.002109608612954617</v>
       </c>
       <c r="W10" t="n">
-        <v>0.009522573091089725</v>
+        <v>0.0006103108171373606</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02739566750824451</v>
+        <v>0.002118655014783144</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002209094818681479</v>
+        <v>0.006951774470508099</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.005415454041212797</v>
+        <v>0.02107598818838596</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001494226162321866</v>
+        <v>0.009527841582894325</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03022113814949989</v>
+        <v>0.003665637224912643</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03962083160877228</v>
+        <v>0.01219541393220425</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0164497010409832</v>
+        <v>0.006150971632450819</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.006669575814157724</v>
+        <v>0.003998584114015102</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02243340387940407</v>
+        <v>0.01587756350636482</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.00339417508803308</v>
+        <v>0.01890087500214577</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01857998967170715</v>
+        <v>0.004376033321022987</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01422618329524994</v>
+        <v>0.02290685847401619</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.009932797402143478</v>
+        <v>0.0003272095927968621</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02970747835934162</v>
+        <v>0.003168984781950712</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0134074417874217</v>
+        <v>0.01563222706317902</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.02082314528524876</v>
+        <v>0.001091855578124523</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02316681481897831</v>
+        <v>0.006183347199112177</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02607635036110878</v>
+        <v>0.009569628164172173</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02256869338452816</v>
+        <v>0.00705725559964776</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.006969815120100975</v>
+        <v>0.01696429774165154</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01801283471286297</v>
+        <v>0.009749981574714184</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.007057785522192717</v>
+        <v>0.005828129127621651</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.007951751351356506</v>
+        <v>0.01024585962295532</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2038003504276276</v>
+        <v>0.01032326370477676</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01672826334834099</v>
+        <v>0.01468572951853275</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.007818042300641537</v>
+        <v>0.0153474435210228</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04617021977901459</v>
+        <v>0.06494522839784622</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02921556308865547</v>
+        <v>0.005019225645810366</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001693299738690257</v>
+        <v>0.00085432268679142</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01173708587884903</v>
+        <v>0.004803911317139864</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.009277801029384136</v>
+        <v>0.009042869322001934</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.008599399589002132</v>
+        <v>0.01123958360403776</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04832945391535759</v>
+        <v>0.003318656235933304</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.03390904143452644</v>
+        <v>0.003564737504348159</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.01378682069480419</v>
+        <v>0.01701274514198303</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.05578285083174706</v>
+        <v>0.01879323087632656</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0540473610162735</v>
+        <v>0.005314097739756107</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.006186834070831537</v>
+        <v>0.0129503458738327</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01178802736103535</v>
+        <v>0.04566090181469917</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0007682396098971367</v>
+        <v>0.0002932026982307434</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.06219055131077766</v>
+        <v>2.816342748701572e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.06564966589212418</v>
+        <v>0.01166058517992496</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0169014073908329</v>
+        <v>0.003196051809936762</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.02423823624849319</v>
+        <v>0.02109056524932384</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.04582008346915245</v>
+        <v>0.0209462083876133</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.009689235128462315</v>
+        <v>0.00961191114038229</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.000237317755818367</v>
+        <v>0.008371719159185886</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.01881792210042477</v>
+        <v>0.003838403150439262</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.01307220011949539</v>
+        <v>0.005042031407356262</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.01341932825744152</v>
+        <v>0.0004032563883811235</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.09624051302671432</v>
+        <v>0.013526925817132</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001652801991440356</v>
+        <v>0.00699637271463871</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01296680700033903</v>
+        <v>0.03793268650770187</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.02185862511396408</v>
+        <v>0.01540057081729174</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.05922902375459671</v>
+        <v>0.001123685156926513</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.01196956634521484</v>
+        <v>0.008517296053469181</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.001315477304160595</v>
+        <v>0.00130949355661869</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.001241632038727403</v>
+        <v>0.01154307369142771</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.01923852413892746</v>
+        <v>0.006745418533682823</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.04362479224801064</v>
+        <v>0.00698632700368762</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001744514680467546</v>
+        <v>0.0009297718061134219</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002018184401094913</v>
+        <v>0.02508996613323689</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01565412059426308</v>
+        <v>0.002746773883700371</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.003040716983377934</v>
+        <v>0.007996806874871254</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.006908662617206573</v>
+        <v>0.008712075650691986</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.001706026960164309</v>
+        <v>0.006774925626814365</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001939332578331232</v>
+        <v>0.002447579521685839</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.04361451044678688</v>
+        <v>0.01959399506449699</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.05547341331839561</v>
+        <v>0.0118099320679903</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02623300068080425</v>
+        <v>0.01129531674087048</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.06113112345337868</v>
+        <v>0.04648951441049576</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.03004314005374908</v>
+        <v>0.02084843069314957</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.04711710661649704</v>
+        <v>0.006636670790612698</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.01511750370264053</v>
+        <v>0.03438081219792366</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01242475770413876</v>
+        <v>0.00889710895717144</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.00730087049305439</v>
+        <v>0.001850459375418723</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01987382769584656</v>
+        <v>0.007170047610998154</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.03376265615224838</v>
+        <v>0.005842544138431549</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.005133287515491247</v>
+        <v>0.001487851841375232</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.009700185619294643</v>
+        <v>0.02847623452544212</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01729426719248295</v>
+        <v>0.005578063894063234</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.007242777850478888</v>
+        <v>0.006282880902290344</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.004417507443577051</v>
+        <v>0.006881781853735447</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.001405116287060082</v>
+        <v>0.004203065298497677</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.001799629535526037</v>
+        <v>0.004184233024716377</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0039143031463027</v>
+        <v>0.01314519718289375</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.02386229299008846</v>
+        <v>0.002373652532696724</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.006423390470445156</v>
+        <v>0.01635804958641529</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.007935442961752415</v>
+        <v>0.04162431508302689</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.004774047993123531</v>
+        <v>0.003612176515161991</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.02223556488752365</v>
+        <v>0.003750886302441359</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01175200752913952</v>
+        <v>0.01316207088530064</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001264994498342276</v>
+        <v>0.03899635374546051</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.001359728863462806</v>
+        <v>0.01021856814622879</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.04081368073821068</v>
+        <v>0.005102268885821104</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01363515667617321</v>
+        <v>0.0009705274133011699</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0235617607831955</v>
+        <v>0.01088169403374195</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.003129258053377271</v>
+        <v>0.02090846747159958</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01551232300698757</v>
+        <v>0.0001232436625286937</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.02014343813061714</v>
+        <v>0.009842412546277046</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.005916137713938951</v>
+        <v>0.0111372796818614</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.01195303723216057</v>
+        <v>0.003230566857382655</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.008380613289773464</v>
+        <v>0.02838513441383839</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.00900446530431509</v>
+        <v>0.0006147469975985587</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.007768982090055943</v>
+        <v>0.005031347274780273</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.02954971417784691</v>
+        <v>0.02372529357671738</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.01532336603850126</v>
+        <v>0.0007430706173181534</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0403805747628212</v>
+        <v>0.0007268549525178969</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.004521227441728115</v>
+        <v>0.008275521919131279</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.00151742179878056</v>
+        <v>0.005361455492675304</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.009816648438572884</v>
+        <v>0.01972998678684235</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.006285716313868761</v>
+        <v>0.002181468531489372</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.02315706387162209</v>
+        <v>0.01557302102446556</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.03992755338549614</v>
+        <v>0.002207134384661913</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02018500678241253</v>
+        <v>0.005404969677329063</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.006514766719192266</v>
+        <v>0.02203210070729256</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.006275380030274391</v>
+        <v>0.01378069631755352</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.00565672991797328</v>
+        <v>0.007458198815584183</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0005222244071774185</v>
+        <v>0.006381263956427574</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.007382438518106937</v>
+        <v>0.00399806909263134</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.001104508759453893</v>
+        <v>7.758635911159217e-05</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01937737129628658</v>
+        <v>0.005708052776753902</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.02504956908524036</v>
+        <v>0.01173949055373669</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.02252486906945705</v>
+        <v>0.006629796698689461</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01761276088654995</v>
+        <v>0.02677348628640175</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01671244017779827</v>
+        <v>0.004197925794869661</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.04132980108261108</v>
+        <v>0.01221208646893501</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01154989376664162</v>
+        <v>0.006594517268240452</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01296834461390972</v>
+        <v>0.004171139560639858</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.01130260899662971</v>
+        <v>0.01188370957970619</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.015044204890728</v>
+        <v>0.007739440072327852</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.03736789524555206</v>
+        <v>0.005955966655164957</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.002222268609330058</v>
+        <v>0.0005854482878930867</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0004503648960962892</v>
+        <v>0.03415178880095482</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.002617383375763893</v>
+        <v>0.005608846433460712</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.01052932441234589</v>
+        <v>0.006900319829583168</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.005678785964846611</v>
+        <v>0.005081526003777981</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.00233086827211082</v>
+        <v>0.004992277361452579</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.00174551410600543</v>
+        <v>0.002500150119885802</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01280849426984787</v>
+        <v>0.00950159877538681</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.009381609037518501</v>
+        <v>5.876112845726311e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.008876415900886059</v>
+        <v>0.00172341288998723</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01134894508868456</v>
+        <v>0.01560784317553043</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.02189917303621769</v>
+        <v>0.001117607811465859</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.005976675543934107</v>
+        <v>0.002910009352490306</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.01145787257701159</v>
+        <v>0.004051781725138426</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0006151739507913589</v>
+        <v>0.003489943686872721</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.007359303534030914</v>
+        <v>0.01253114547580481</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01295578945428133</v>
+        <v>0.01982708275318146</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.04012582451105118</v>
+        <v>0.0356433279812336</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.005019864067435265</v>
+        <v>0.009667646139860153</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.05141428858041763</v>
+        <v>0.007616829127073288</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.03677699342370033</v>
+        <v>0.006748887244611979</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.02067713625729084</v>
+        <v>0.03164118528366089</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.01605271548032761</v>
+        <v>0.01789990626275539</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01300233416259289</v>
+        <v>0.01447191741317511</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.003006411716341972</v>
+        <v>0.01102422922849655</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.02649633400142193</v>
+        <v>0.004429839551448822</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02968334034085274</v>
+        <v>0.0009410518687218428</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.005743476562201977</v>
+        <v>0.01832763105630875</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.01049993839114904</v>
+        <v>0.0254051499068737</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.02013189904391766</v>
+        <v>0.001896224566735327</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.01911163702607155</v>
+        <v>0.002371563576161861</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.02049378864467144</v>
+        <v>0.001159370876848698</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.01362972799688578</v>
+        <v>0.002815324813127518</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0001352491672150791</v>
+        <v>0.01351071335375309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.001596813555806875</v>
+        <v>0.001440516673028469</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01171424519270658</v>
+        <v>0.00441953307017684</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001413624617271125</v>
+        <v>0.001418889150954783</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003526831977069378</v>
+        <v>0.00391958886757493</v>
       </c>
       <c r="E11" t="n">
-        <v>0.007263709791004658</v>
+        <v>0.004257780965417624</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0003590238047763705</v>
+        <v>0.007081770338118076</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0008427085122093558</v>
+        <v>0.001696519553661346</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003809357294812799</v>
+        <v>0.004474625457078218</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001171751180663705</v>
+        <v>0.0002629170485306531</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001328551443293691</v>
+        <v>0.0009576281299814582</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009504225105047226</v>
+        <v>0.006204345263540745</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001958364446181804</v>
+        <v>0.0004154348280280828</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0006223588716238737</v>
+        <v>0.001776526216417551</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003624770790338516</v>
+        <v>0.008513043634593487</v>
       </c>
       <c r="O11" t="n">
-        <v>0.000176630390342325</v>
+        <v>0.008723984472453594</v>
       </c>
       <c r="P11" t="n">
-        <v>1.842866186052561e-05</v>
+        <v>0.0005203685723245144</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0008485972066409886</v>
+        <v>0.001223192550241947</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002899063751101494</v>
+        <v>0.001614671666175127</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003794171207118779</v>
+        <v>0.002705209190025926</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0006147990934550762</v>
+        <v>0.001505802618339658</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0004547295393422246</v>
+        <v>0.002287833951413631</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001576580805703998</v>
+        <v>0.001397687243297696</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006440449040383101</v>
+        <v>0.00141412578523159</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001006549573503435</v>
+        <v>0.001626567100174725</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0004034311859868467</v>
+        <v>0.001023903605528176</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.003226657165214419</v>
+        <v>0.001640724018216133</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0008637195569463074</v>
+        <v>0.0005084395525045693</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.000286542228423059</v>
+        <v>0.004050188697874546</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001493032905273139</v>
+        <v>0.001143908360973001</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.264265928417444e-05</v>
+        <v>0.0003302853438071907</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001101010479032993</v>
+        <v>0.001336061395704746</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0004230243503116071</v>
+        <v>0.003200685139745474</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0001207602326758206</v>
+        <v>0.002915442455559969</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.396167838014662e-05</v>
+        <v>0.003469635499641299</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0001806276850402355</v>
+        <v>0.004474630113691092</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0009116424480453134</v>
+        <v>0.0007643501739948988</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.001242373837158084</v>
+        <v>0.00240977993234992</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001666502212174237</v>
+        <v>0.002358486410230398</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0009439195855520666</v>
+        <v>0.001259316690266132</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0008261972106993198</v>
+        <v>0.001452088938094676</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001895251916721463</v>
+        <v>0.00112410809379071</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.002309350296854973</v>
+        <v>0.0005923346616327763</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0006608681287616491</v>
+        <v>0.0009051063098013401</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.206057827919722e-05</v>
+        <v>0.001262500416487455</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0005312315770424902</v>
+        <v>0.000353174633346498</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0004132073954679072</v>
+        <v>0.001575760310515761</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.007702998351305723</v>
+        <v>0.01096516661345959</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0003247282584197819</v>
+        <v>0.001160900574177504</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001974695129320025</v>
+        <v>0.001525709754787385</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.00404562521725893</v>
+        <v>0.001782755134627223</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003652294399216771</v>
+        <v>0.004768813028931618</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.004931209143251181</v>
+        <v>0.002146294573321939</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001134865684434772</v>
+        <v>0.0009288002620451152</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0005519299302250147</v>
+        <v>0.001056844834238291</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.002416904084384441</v>
+        <v>0.002483671763911843</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.004452326335012913</v>
+        <v>0.002361906226724386</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0010916693136096</v>
+        <v>0.0005742600187659264</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.000709717336576432</v>
+        <v>0.004733163397759199</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.001716520870104432</v>
+        <v>0.001165050314739347</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0002940949343610555</v>
+        <v>0.0008963829022832215</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.002915822435170412</v>
+        <v>0.0001907401601783931</v>
       </c>
       <c r="BJ11" t="n">
-        <v>7.745582843199372e-05</v>
+        <v>0.004075950942933559</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0008745481027290225</v>
+        <v>0.001804779749363661</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002605873625725508</v>
+        <v>0.001122190617024899</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.003307797713205218</v>
+        <v>0.003906384110450745</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0005959381815046072</v>
+        <v>0.0004810282262042165</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.003292622976005077</v>
+        <v>0.001382357673719525</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0005236042197793722</v>
+        <v>0.003726294729858637</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.001830838969908655</v>
+        <v>0.004368429072201252</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0007422063499689102</v>
+        <v>0.0007018005126155913</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.002287036273628473</v>
+        <v>0.001523886574432254</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.001074338797479868</v>
+        <v>0.001861552009359002</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0001314638066105545</v>
+        <v>0.001681904192082584</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.00532008521258831</v>
+        <v>0.006519626826047897</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002088294830173254</v>
+        <v>0.0005175748956389725</v>
       </c>
       <c r="BX11" t="n">
-        <v>7.266981992870569e-05</v>
+        <v>0.005305011756718159</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0009923777543008327</v>
+        <v>0.0009248097194358706</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0009546208893880248</v>
+        <v>0.00204375758767128</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.001215180149301887</v>
+        <v>0.0001620808325242251</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.001586763886734843</v>
+        <v>0.001191888703033328</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0001566713326610625</v>
+        <v>0.0007194183999672532</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0002531936625018716</v>
+        <v>0.002712565241381526</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.001481507904827595</v>
+        <v>0.001828055828809738</v>
       </c>
       <c r="CF11" t="n">
-        <v>6.508903607027605e-05</v>
+        <v>0.001051621744409204</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0001590994215803221</v>
+        <v>0.0004526925040408969</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.00111767603084445</v>
+        <v>0.0008409456931985915</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0001361432368867099</v>
+        <v>0.002129797823727131</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001074089435860515</v>
+        <v>0.0005745916860178113</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001489582238718867</v>
+        <v>0.0001533968461444601</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0005573011585511267</v>
+        <v>0.0002712615532800555</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.002017251448705792</v>
+        <v>0.002153021283447742</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.002271316479891539</v>
+        <v>0.005965498741716146</v>
       </c>
       <c r="CO11" t="n">
-        <v>3.575056325644255e-05</v>
+        <v>0.001060580252669752</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.003284364240244031</v>
+        <v>0.001469178008846939</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001860988442786038</v>
+        <v>0.001553582958877087</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0001926526892930269</v>
+        <v>0.001019118237309158</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0028772356454283</v>
+        <v>0.002706208499148488</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001023621996864676</v>
+        <v>0.0001238155673490837</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0013985859695822</v>
+        <v>0.0006291919853538275</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.56734638242051e-05</v>
+        <v>0.002212559804320335</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.00112190458457917</v>
+        <v>0.001106727635487914</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0003762307169381529</v>
+        <v>0.0005250242538750172</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0005880983080714941</v>
+        <v>0.0001232876093126833</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002820236841216683</v>
+        <v>0.001047269091941416</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0005304284859448671</v>
+        <v>0.002182229422032833</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0006299938540905714</v>
+        <v>5.849612352903932e-05</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.001393337734043598</v>
+        <v>0.0005107131437398493</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0007501783547922969</v>
+        <v>0.0001564706617500633</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.002420478966087103</v>
+        <v>0.00117351277731359</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0009449327480979264</v>
+        <v>0.00187007780186832</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0007113237516023219</v>
+        <v>0.0008360790670849383</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.006814128719270229</v>
+        <v>0.0008387360721826553</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.004033717326819897</v>
+        <v>0.001452628523111343</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.004919940140098333</v>
+        <v>0.002201503608375788</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.002233582083135843</v>
+        <v>0.001705663744360209</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0001933275489136577</v>
+        <v>0.005818948149681091</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.004499836359173059</v>
+        <v>0.003945286385715008</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0002607733476907015</v>
+        <v>0.002258535707369447</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0006194089073687792</v>
+        <v>2.625049091875553e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001160170999355614</v>
+        <v>4.664261359721422e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.001446157926693559</v>
+        <v>0.002082805847749114</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.002482602838426828</v>
+        <v>0.001888443017378449</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0007388483500108123</v>
+        <v>0.002186263911426067</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.002031483221799135</v>
+        <v>0.0001623492571525276</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0007706575561314821</v>
+        <v>0.002113335998728871</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.001934430445544422</v>
+        <v>0.0003370559425093234</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0004662536957766861</v>
+        <v>0.0002767810074146837</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0008276054868474603</v>
+        <v>0.000697669165674597</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001003976329229772</v>
+        <v>2.922816202044487e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001766706467606127</v>
+        <v>0.001741363666951656</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.001144936075434089</v>
+        <v>0.00322280265390873</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0006308764568530023</v>
+        <v>0.001182492822408676</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.000400224031182006</v>
+        <v>0.0001491155417170376</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0007815513527020812</v>
+        <v>0.001056295121088624</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.002918141195550561</v>
+        <v>0.002932448638603091</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0002456779475323856</v>
+        <v>0.001965172123163939</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.002103104488924146</v>
+        <v>0.0009350818581879139</v>
       </c>
       <c r="EH11" t="n">
-        <v>2.284253423567861e-05</v>
+        <v>0.001089364639483392</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.00095541583141312</v>
+        <v>0.0001693167432677001</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001146750641055405</v>
+        <v>0.001056701526977122</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.002545284107327461</v>
+        <v>0.002432778477668762</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.000935823773033917</v>
+        <v>0.0002784985699690878</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001449424307793379</v>
+        <v>0.0006806878955103457</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0005184239707887173</v>
+        <v>0.000568944204133004</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0008969617774710059</v>
+        <v>0.002592699602246284</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0001031300780596212</v>
+        <v>0.001335536362603307</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001335575361736119</v>
+        <v>0.0006147738895379007</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.001847436768002808</v>
+        <v>0.001230641384609044</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0004751500091515481</v>
+        <v>0.002457053866237402</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001085978001356125</v>
+        <v>0.0001410107943229377</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001849342021159828</v>
+        <v>0.0007551414892077446</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.003019218798726797</v>
+        <v>0.002089320449158549</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0009659380884841084</v>
+        <v>0.0002888173330575228</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001887803664430976</v>
+        <v>0.002804646966978908</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0009558813762851059</v>
+        <v>0.001755336299538612</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0001279408897971734</v>
+        <v>0.0006284726550802588</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0001462245709262788</v>
+        <v>0.0002104583545587957</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0006979441968724132</v>
+        <v>0.0002419041702523828</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0001630338956601918</v>
+        <v>0.001709923380985856</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001559758791700006</v>
+        <v>0.0004896941245533526</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001929800026118755</v>
+        <v>0.000400553981307894</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001251068199053407</v>
+        <v>0.00096153374761343</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0009427057229913771</v>
+        <v>0.0002470622712280601</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0007954261382110417</v>
+        <v>0.001609671046026051</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0001918741036206484</v>
+        <v>3.891566302627325e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.003001077799126506</v>
+        <v>0.003605460980907083</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.000767122081015259</v>
+        <v>0.0007776733837090433</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0001571149914525449</v>
+        <v>0.0009730385500006378</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.00245130923576653</v>
+        <v>0.001291290041990578</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0008643123437650502</v>
+        <v>0.003512563649564981</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0004644480650313199</v>
+        <v>0.0003622825024649501</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.002258219756186008</v>
+        <v>0.0004328147624619305</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0001662043505348265</v>
+        <v>0.002898231381550431</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.001139263738878071</v>
+        <v>0.0005232037510722876</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.00204917648807168</v>
+        <v>0.001463786233216524</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.008446363732218742</v>
+        <v>0.001324860728345811</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.002414369024336338</v>
+        <v>0.00153431692160666</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.002667389577254653</v>
+        <v>0.0001231032947544008</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0003807379980571568</v>
+        <v>0.004407803528010845</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.001619589631445706</v>
+        <v>0.002443374134600163</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001746501424349844</v>
+        <v>0.003743018722161651</v>
       </c>
       <c r="FZ11" t="n">
-        <v>6.682051753159612e-05</v>
+        <v>0.0007701269933022559</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.001590198138728738</v>
+        <v>0.001956106163561344</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.002496897941455245</v>
+        <v>0.000409739906899631</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0007730286451987922</v>
+        <v>0.0007962823146954179</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.002642599167302251</v>
+        <v>0.002504217205569148</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.00109953002538532</v>
+        <v>0.001298729795962572</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.002107535023242235</v>
+        <v>0.001305710757151246</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.001659813802689314</v>
+        <v>0.002012759214267135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0006989692337810993</v>
+        <v>3.964707866543904e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009226294234395027</v>
+        <v>0.001385600888170302</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007140214438550174</v>
+        <v>0.0001769232767401263</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00582248717546463</v>
+        <v>0.001730861142277718</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001542775542475283</v>
+        <v>0.0005250668036751449</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001232482027262449</v>
+        <v>0.001817245851270854</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0009125530486926436</v>
+        <v>0.001379731460474432</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001154612982645631</v>
+        <v>0.001679820124991238</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002062175481114537</v>
+        <v>0.0003394012455828488</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00117176934145391</v>
+        <v>9.873992530629039e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006148694083094597</v>
+        <v>0.0009076615097001195</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002607068745419383</v>
+        <v>0.0003848453925456852</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005549207795411348</v>
+        <v>0.002519085770472884</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002741928678005934</v>
+        <v>0.001413368037901819</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002778361085802317</v>
+        <v>0.001975832507014275</v>
       </c>
       <c r="P12" t="n">
-        <v>3.540335455909371e-05</v>
+        <v>0.001462802174501121</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0007126774871721864</v>
+        <v>0.001135128433816135</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0006480295560322702</v>
+        <v>9.69750908552669e-05</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001415265287505463</v>
+        <v>0.0001375349384034052</v>
       </c>
       <c r="T12" t="n">
-        <v>0.001602254807949066</v>
+        <v>4.969975270796567e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0004066269029863179</v>
+        <v>0.0004344393673818558</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0008173953392542899</v>
+        <v>0.0002092848881147802</v>
       </c>
       <c r="W12" t="n">
-        <v>7.280464342329651e-05</v>
+        <v>0.0003604141820687801</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0009988001547753811</v>
+        <v>0.0005287601379677653</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.001093658385798335</v>
+        <v>9.7375173936598e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0002038793318206444</v>
+        <v>0.0001626989105716348</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0006463974714279175</v>
+        <v>0.0001076607513823546</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0006642099469900131</v>
+        <v>0.0001608952588867396</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.002131331246346235</v>
+        <v>0.0004165198188275099</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.965669308556244e-05</v>
+        <v>0.0003132307319901884</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0005335377645678818</v>
+        <v>0.0004435032897163182</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0004677998367697001</v>
+        <v>0.00075070362072438</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0003025155747309327</v>
+        <v>0.0007655984372831881</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0009486065246164799</v>
+        <v>0.0003561254707165062</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0003062270407099277</v>
+        <v>0.0004356211866252124</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0001192480849567801</v>
+        <v>0.0003808239125646651</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0005458472296595573</v>
+        <v>0.0001904874516185373</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0008980257553048432</v>
+        <v>0.0007287712069228292</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.000382826488930732</v>
+        <v>0.0006436452968046069</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0004272355581633747</v>
+        <v>0.0003923055483028293</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.001102529582567513</v>
+        <v>0.0001413908030372113</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.001036478439345956</v>
+        <v>0.0005852730246260762</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0004128387372475117</v>
+        <v>0.0004062020743731409</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.000585025642067194</v>
+        <v>0.0001466600806452334</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0002193879772676155</v>
+        <v>9.080865129362792e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0008168036583811045</v>
+        <v>0.0005645131459459662</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.006888722069561481</v>
+        <v>0.0007466601673513651</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001576065842527896</v>
+        <v>0.000884341774508357</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0003635702305473387</v>
+        <v>0.000251164601650089</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0007826011278666556</v>
+        <v>0.002115725073963404</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0002952939830720425</v>
+        <v>0.001477668411098421</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0003302490222267807</v>
+        <v>0.0001309186627622694</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0006167604587972164</v>
+        <v>2.430387030472048e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.921500708907843e-06</v>
+        <v>0.0003886041522491723</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0001387812226312235</v>
+        <v>9.459356078878045e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.001527835614979267</v>
+        <v>0.000297870923532173</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.001668585347943008</v>
+        <v>0.0002240967151010409</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.001243049511685967</v>
+        <v>0.0003150639531668276</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.003002310404554009</v>
+        <v>0.0006492814864031971</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0008654291741549969</v>
+        <v>0.0001333300897385925</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.001526081701740623</v>
+        <v>0.0004619094834197313</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0006731722969561815</v>
+        <v>0.0007974788313731551</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0007523162639699876</v>
+        <v>0.0002232364640804008</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.001353282015770674</v>
+        <v>0.0002231553953606635</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.00172824424225837</v>
+        <v>0.0004264311864972115</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0007741301669739187</v>
+        <v>4.892579454462975e-06</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.406397394835949e-05</v>
+        <v>0.0004741919983644038</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.001270269392989576</v>
+        <v>0.0003627486294135451</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0007580583915114403</v>
+        <v>7.186596485553309e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.001235696487128735</v>
+        <v>0.0001603712153155357</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.001175423851236701</v>
+        <v>0.0001002241333480924</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.745573899825104e-05</v>
+        <v>0.0001624597935006022</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0005194622790440917</v>
+        <v>0.0002696742303669453</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.003515108488500118</v>
+        <v>0.0007493821321986616</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0006395488162524998</v>
+        <v>0.0004228910256642848</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0006562807830050588</v>
+        <v>0.0007617008523084223</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0003537091834004968</v>
+        <v>0.0004466302343644202</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.001461514388211071</v>
+        <v>0.0009485918562859297</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0002634600969031453</v>
+        <v>0.0002830952289514244</v>
       </c>
       <c r="CB12" t="n">
-        <v>8.30933713587001e-05</v>
+        <v>5.156432598596439e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0005813585012219846</v>
+        <v>0.00014628199278377</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0004487426485866308</v>
+        <v>2.622932879603468e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.00162563577760011</v>
+        <v>0.0003734150668606162</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0004430122207850218</v>
+        <v>4.273580270819366e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0003248611174058169</v>
+        <v>0.0006687995046377182</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0004712497757282108</v>
+        <v>0.0001862834906205535</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0003151818818878382</v>
+        <v>0.0003836479445453733</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0006178950425237417</v>
+        <v>6.151021807454526e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>6.088045483920723e-05</v>
+        <v>0.0004063993110321462</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0003508150693960488</v>
+        <v>0.0001303179597016424</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.001389622688293457</v>
+        <v>0.0004534703330136836</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.001029359409585595</v>
+        <v>0.0004025458183605224</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0004653812502510846</v>
+        <v>0.0008602684829384089</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.002596603473648429</v>
+        <v>0.001146446913480759</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.001210420508868992</v>
+        <v>0.0007409573881886899</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.001515459967777133</v>
+        <v>0.0003211956936866045</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.001080835703760386</v>
+        <v>0.000566910021007061</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.001213500625453889</v>
+        <v>8.645786147098988e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>3.513351839501411e-05</v>
+        <v>0.0002095846430165693</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0004416158772073686</v>
+        <v>9.923161996994168e-06</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.001224587205797434</v>
+        <v>0.0002734073786996305</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0005930960178375244</v>
+        <v>1.23061727208551e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0007395243155770004</v>
+        <v>0.0007084221579134464</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0004948124405927956</v>
+        <v>0.0004298848216421902</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0004473754088394344</v>
+        <v>0.0003839267301373184</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0007029549451544881</v>
+        <v>1.226926542585716e-06</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0001176403893623501</v>
+        <v>0.0003730937605723739</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0001826300867833197</v>
+        <v>0.0001687608746578917</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0005524876760318875</v>
+        <v>0.0003164021181873977</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.001792659400962293</v>
+        <v>0.0001413847057847306</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0001651353668421507</v>
+        <v>0.0002115014649461955</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.002382725942879915</v>
+        <v>0.0005086957244202495</v>
       </c>
       <c r="DI12" t="n">
-        <v>9.187134855892509e-05</v>
+        <v>9.072342800209299e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0007717520347796381</v>
+        <v>0.000934372132178396</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0009029615321196616</v>
+        <v>7.681232818868011e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>6.242634844966233e-05</v>
+        <v>0.001220353064127266</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0002924124128185213</v>
+        <v>0.0002308953407919034</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0008530020713806152</v>
+        <v>0.0001863479556050152</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.000648122513666749</v>
+        <v>0.0005314016598276794</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0007941269432194531</v>
+        <v>0.0001370655954815447</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0008935398072935641</v>
+        <v>0.0001099982619052753</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.001447067479602993</v>
+        <v>0.0001688698539510369</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0006498487782664597</v>
+        <v>0.0002921984414570034</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.00023607250477653</v>
+        <v>0.0001889791456051171</v>
       </c>
       <c r="DU12" t="n">
-        <v>3.513009869493544e-05</v>
+        <v>0.0005604507168754935</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0004677042888943106</v>
+        <v>0.0008505320874974132</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0001934727770276368</v>
+        <v>0.0001333957043243572</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0002600661828182638</v>
+        <v>0.0001701537257758901</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.001023119664750993</v>
+        <v>0.0007891496643424034</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0008443128899671137</v>
+        <v>0.0003185269888490438</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0009857567492872477</v>
+        <v>0.000342933984939009</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0004645442822948098</v>
+        <v>0.000319415150443092</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0004521984665188938</v>
+        <v>0.0001702722511254251</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0002334083401365206</v>
+        <v>0.0007924054516479373</v>
       </c>
       <c r="EE12" t="n">
-        <v>3.607679536798969e-05</v>
+        <v>0.0007494791643694043</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0001347138022538275</v>
+        <v>0.0002000086824409664</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0007523916428908706</v>
+        <v>0.0001140048989327624</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0001326356141362339</v>
+        <v>0.000473928201245144</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0004268220509402454</v>
+        <v>0.0007517475169152021</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.001119663938879967</v>
+        <v>0.0003413938102312386</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0002527464530430734</v>
+        <v>0.0003399568377062678</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.001170510076917708</v>
+        <v>5.482534470502287e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0003425769973546267</v>
+        <v>0.0003034913970623165</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0001587755104992539</v>
+        <v>1.076608896255493e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.000637699558865279</v>
+        <v>8.953443466452882e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.001198132173158228</v>
+        <v>0.0005309124244377017</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001690247445367277</v>
+        <v>1.673816586844623e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0006382724968716502</v>
+        <v>0.0008036624640226364</v>
       </c>
       <c r="ES12" t="n">
-        <v>6.735114584444091e-05</v>
+        <v>6.470715015893802e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001648156205192208</v>
+        <v>3.786553861573339e-07</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.00115307979285717</v>
+        <v>0.0003279502270743251</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0003164882946293801</v>
+        <v>0.0003716333594638854</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001399538305122405</v>
+        <v>0.0007757643470540643</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0002286451635882258</v>
+        <v>1.584025994816329e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.001264983555302024</v>
+        <v>0.0004552023601718247</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0002460602554492652</v>
+        <v>4.637645906768739e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0007041941862553358</v>
+        <v>0.0007828574744053185</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0002548884658608586</v>
+        <v>0.0002758853370323777</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0006539850728586316</v>
+        <v>0.0004379501042421907</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.000732446787878871</v>
+        <v>5.220625826041214e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>4.55762492492795e-05</v>
+        <v>0.0004015062586404383</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.000346070621162653</v>
+        <v>5.817055352963507e-07</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0001002150238491595</v>
+        <v>0.0003260414232499897</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0001535755873192102</v>
+        <v>1.598408562131226e-05</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0004330612136982381</v>
+        <v>0.000343768741004169</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001304011093452573</v>
+        <v>5.432084435597062e-07</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0006424051243811846</v>
+        <v>0.0001330294326180592</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0004331038217060268</v>
+        <v>0.0001258704287465662</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0005288374377414584</v>
+        <v>0.0004129676381126046</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0001051258441293612</v>
+        <v>0.000613786221947521</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0002674772695172578</v>
+        <v>0.0003679684014059603</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0003571242559701204</v>
+        <v>0.000393006659578532</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0005395807093009353</v>
+        <v>0.000493835483212024</v>
       </c>
       <c r="FR12" t="n">
-        <v>2.798876812448725e-05</v>
+        <v>0.001238299533724785</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001148442155681551</v>
+        <v>0.0002419918746454641</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001194417010992765</v>
+        <v>0.0008502997225150466</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0001695644168648869</v>
+        <v>0.0001088265198632143</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.001498902216553688</v>
+        <v>0.0005182875320315361</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0006542821647599339</v>
+        <v>0.001693001948297024</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0002799475332722068</v>
+        <v>0.000180564122274518</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.001236445736140013</v>
+        <v>7.711496436968446e-07</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0004428458050824702</v>
+        <v>0.0002003127592615783</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0001663663570070639</v>
+        <v>0.0003901809104718268</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0001624542928766459</v>
+        <v>0.0005838643992319703</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.001046076416969299</v>
+        <v>6.578320608241484e-05</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0009668123675510287</v>
+        <v>0.0009423224255442619</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.002265438437461853</v>
+        <v>0.0005081772105768323</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0004421182384248823</v>
+        <v>0.0003276707429904491</v>
       </c>
       <c r="GG12" t="n">
-        <v>6.308688898570836e-05</v>
+        <v>0.0002712854475248605</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.006668403744697571</v>
+        <v>0.01198680885136127</v>
       </c>
       <c r="B13" t="n">
-        <v>0.07436509430408478</v>
+        <v>0.08872881531715393</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005545240361243486</v>
+        <v>0.004263076465576887</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02564850822091103</v>
+        <v>0.06839310377836227</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008024401031434536</v>
+        <v>0.03412729501724243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06869199872016907</v>
+        <v>0.06389711797237396</v>
       </c>
       <c r="G13" t="n">
-        <v>0.012015325948596</v>
+        <v>0.03258704021573067</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04403389990329742</v>
+        <v>0.02225169166922569</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0105522945523262</v>
+        <v>0.002890341449528933</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01711656153202057</v>
+        <v>0.001198329031467438</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07432322949171066</v>
+        <v>0.1342443376779556</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006251698359847069</v>
+        <v>0.01196324080228806</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01290363539010286</v>
+        <v>0.09313233941793442</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02920936420559883</v>
+        <v>0.04518879950046539</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05327323824167252</v>
+        <v>0.09090511500835419</v>
       </c>
       <c r="P13" t="n">
-        <v>0.006893556099385023</v>
+        <v>0.03869567438960075</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02018610388040543</v>
+        <v>0.01308381929993629</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02128804475069046</v>
+        <v>0.008591083809733391</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0006555116269737482</v>
+        <v>0.0008956925012171268</v>
       </c>
       <c r="T13" t="n">
-        <v>0.007700306829065084</v>
+        <v>0.01820298843085766</v>
       </c>
       <c r="U13" t="n">
-        <v>0.004270361736416817</v>
+        <v>0.02431412786245346</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01232142653316259</v>
+        <v>0.0627429187297821</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03304211795330048</v>
+        <v>0.1063043251633644</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01899095252156258</v>
+        <v>0.04705754294991493</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002821171656250954</v>
+        <v>0.01932614855468273</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01663496159017086</v>
+        <v>0.008993351832032204</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01138002332299948</v>
+        <v>0.02772939205169678</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.002255072351545095</v>
+        <v>0.03590260818600655</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.002244188450276852</v>
+        <v>0.01172447763383389</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.006509889848530293</v>
+        <v>0.004482004791498184</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.006402214057743549</v>
+        <v>0.005382934585213661</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01057419180870056</v>
+        <v>0.04008392244577408</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01262411847710609</v>
+        <v>0.05265156924724579</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.003411320503801107</v>
+        <v>0.02186330407857895</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.00962268840521574</v>
+        <v>0.02329014241695404</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001101217581890523</v>
+        <v>0.03913341462612152</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.009303547441959381</v>
+        <v>0.01344293728470802</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.001157974009402096</v>
+        <v>0.01113869063556194</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003892143722623587</v>
+        <v>0.000890267314389348</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.009653338231146336</v>
+        <v>0.03904090076684952</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.00120632559992373</v>
+        <v>0.03325873985886574</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.009874818846583366</v>
+        <v>0.01656165905296803</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.003935265354812145</v>
+        <v>0.009511265903711319</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.005948964506387711</v>
+        <v>0.04786670207977295</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.006686959881335497</v>
+        <v>0.02211572974920273</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.006955159828066826</v>
+        <v>0.02658508531749249</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0317300409078598</v>
+        <v>0.1802501082420349</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001418474363163114</v>
+        <v>0.02445576712489128</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.01615012623369694</v>
+        <v>0.03390264511108398</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.01191804651170969</v>
+        <v>0.0051008565351367</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.04088202491402626</v>
+        <v>0.04204526916146278</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02675803937017918</v>
+        <v>0.03594207763671875</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001873257104307413</v>
+        <v>0.03540050238370895</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.01847634464502335</v>
+        <v>0.02509034052491188</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0002895854413509369</v>
+        <v>0.0152048273012042</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03080883994698524</v>
+        <v>0.02537280879914761</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01706183701753616</v>
+        <v>0.02228666469454765</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.005131551064550877</v>
+        <v>0.02617000788450241</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01016821153461933</v>
+        <v>0.02017421275377274</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.007661852985620499</v>
+        <v>0.04628116637468338</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01169611513614655</v>
+        <v>0.06840656697750092</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.00677183223888278</v>
+        <v>0.01346920151263475</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01683790795505047</v>
+        <v>0.001035877503454685</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.009502079337835312</v>
+        <v>0.02209512516856194</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.01106343697756529</v>
+        <v>0.02706905268132687</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.009215742349624634</v>
+        <v>0.0003447611816227436</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01517121680080891</v>
+        <v>0.02467916160821915</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.001837381161749363</v>
+        <v>0.00294003589078784</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.00109958543907851</v>
+        <v>0.003839144017547369</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.002075224183499813</v>
+        <v>0.07576555013656616</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.01092466805130243</v>
+        <v>0.01952089928090572</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.004042309708893299</v>
+        <v>0.01879492960870266</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.002270722528919578</v>
+        <v>0.01432026363909245</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02620181813836098</v>
+        <v>0.08591320365667343</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.004009724128991365</v>
+        <v>0.01719304174184799</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.005787181667983532</v>
+        <v>0.06714895367622375</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.002322605345398188</v>
+        <v>0.09940534830093384</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.02224892191588879</v>
+        <v>0.07630753517150879</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.007556440308690071</v>
+        <v>0.006220422685146332</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002239118330180645</v>
+        <v>0.0124907623976469</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.008973110467195511</v>
+        <v>0.03780423849821091</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001413051155395806</v>
+        <v>0.01157392468303442</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01151694264262915</v>
+        <v>0.03102389350533485</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.007893618196249008</v>
+        <v>0.001230615889653563</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0007891132845543325</v>
+        <v>0.01207361649721861</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0004229092737659812</v>
+        <v>0.003370331600308418</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0109174195677042</v>
+        <v>0.02869433350861073</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.006090897601097822</v>
+        <v>0.02392044849693775</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.00745122879743576</v>
+        <v>0.009746536612510681</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.008168548345565796</v>
+        <v>0.003789480309933424</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.008044414222240448</v>
+        <v>0.04315304011106491</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.009129186160862446</v>
+        <v>0.1017986759543419</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001618812326341867</v>
+        <v>0.0008762947982177138</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0231110155582428</v>
+        <v>0.000275920145213604</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.002726251259446144</v>
+        <v>0.0633653923869133</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.006487168837338686</v>
+        <v>0.08532845973968506</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.02073783241212368</v>
+        <v>0.02514549717307091</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01193671859800816</v>
+        <v>0.04284829646348953</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.008274518884718418</v>
+        <v>0.04220148175954819</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001535897143185139</v>
+        <v>0.01663416437804699</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01090605743229389</v>
+        <v>0.02749983966350555</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.006893571931868792</v>
+        <v>0.00174975348636508</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.001925122807733715</v>
+        <v>0.005672818049788475</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.002620539627969265</v>
+        <v>0.00478247320279479</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.009740764275193214</v>
+        <v>0.01718230172991753</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.005668783560395241</v>
+        <v>0.01488125417381525</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.01022195816040039</v>
+        <v>0.01137749198824167</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.005974418018013239</v>
+        <v>0.0001853201538324356</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.007460814900696278</v>
+        <v>0.002498092129826546</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.006765902042388916</v>
+        <v>0.01708324998617172</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.001731354859657586</v>
+        <v>0.03175656124949455</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.03922417759895325</v>
+        <v>0.001774614676833153</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01586618646979332</v>
+        <v>0.01429053768515587</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03595505282282829</v>
+        <v>0.03300952538847923</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.003504113294184208</v>
+        <v>0.04067320376634598</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.01437319256365299</v>
+        <v>0.000176604837179184</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02080123126506805</v>
+        <v>0.0669240728020668</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.002856663893908262</v>
+        <v>0.01794102974236012</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001231912756338716</v>
+        <v>0.007681068032979965</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.01355362124741077</v>
+        <v>0.001036569243296981</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.006637908983975649</v>
+        <v>0.07908778637647629</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01414972171187401</v>
+        <v>0.02238717675209045</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.007881633937358856</v>
+        <v>0.02467747405171394</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.005905959755182266</v>
+        <v>0.003093268722295761</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.002085826359689236</v>
+        <v>0.03786716982722282</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0008369003189727664</v>
+        <v>0.003874058835208416</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.00282186409458518</v>
+        <v>0.02074790000915527</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.004146930761635303</v>
+        <v>0.01845732890069485</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.002978825941681862</v>
+        <v>0.01662064902484417</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.007447374984622002</v>
+        <v>0.04902568459510803</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.009036692790687084</v>
+        <v>0.02130530215799809</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01994596421718597</v>
+        <v>0.0392720066010952</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.002632936928421259</v>
+        <v>0.02183777466416359</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.008120124228298664</v>
+        <v>0.03262129426002502</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.02032203786075115</v>
+        <v>0.002485435456037521</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002674086717888713</v>
+        <v>0.01437391899526119</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01745259761810303</v>
+        <v>0.01195797603577375</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.006596813444048166</v>
+        <v>0.001781458035111427</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0106451129540801</v>
+        <v>0.03133100271224976</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.003485932946205139</v>
+        <v>0.0223646555095911</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.003170066978782415</v>
+        <v>0.00183535588439554</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.003686295123770833</v>
+        <v>0.002516188658773899</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.004979482851922512</v>
+        <v>0.0008856058702804148</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.004491479136049747</v>
+        <v>0.01694102585315704</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001662431750446558</v>
+        <v>0.008103394880890846</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.008004847913980484</v>
+        <v>0.001805088715627789</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.000109698623418808</v>
+        <v>0.01176261529326439</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.005570976994931698</v>
+        <v>0.01332322042435408</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0009377645910717547</v>
+        <v>0.01513394434005022</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01255292259156704</v>
+        <v>0.02944429963827133</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.01549369283020496</v>
+        <v>0.01764412969350815</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.03090780600905418</v>
+        <v>0.02865399233996868</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.004261529073119164</v>
+        <v>0.006861750036478043</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0008755797753110528</v>
+        <v>0.01634851656854153</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.008123734034597874</v>
+        <v>0.03715569153428078</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.004141787067055702</v>
+        <v>0.001489050919190049</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001812382834032178</v>
+        <v>0.0006997506134212017</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004472598666325212</v>
+        <v>0.00240621529519558</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.008538141846656799</v>
+        <v>0.0262850746512413</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.01103303581476212</v>
+        <v>0.02651195973157883</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01034278981387615</v>
+        <v>0.009176927618682384</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.008483957499265671</v>
+        <v>0.00492095248773694</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.008727069012820721</v>
+        <v>0.01231709774583578</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.005636177957057953</v>
+        <v>0.04249522089958191</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.005406943149864674</v>
+        <v>0.01354381628334522</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01629508659243584</v>
+        <v>0.03622566163539886</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0006384670850820839</v>
+        <v>0.003363872645422816</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.007650021463632584</v>
+        <v>0.0349632166326046</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.01019397657364607</v>
+        <v>0.01130322739481926</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.005154778249561787</v>
+        <v>0.01353157311677933</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.002884628949686885</v>
+        <v>0.0008482076227664948</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.005010892637073994</v>
+        <v>0.01820934750139713</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01303553581237793</v>
+        <v>0.1059283018112183</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01254836563020945</v>
+        <v>0.001137887826189399</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0137470243498683</v>
+        <v>0.06189876422286034</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.03122126497328281</v>
+        <v>0.06993237882852554</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.02048872411251068</v>
+        <v>0.02788275294005871</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01612201519310474</v>
+        <v>0.05248016864061356</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.008819630369544029</v>
+        <v>0.00575847364962101</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01146269403398037</v>
+        <v>0.03860721364617348</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0136419702321291</v>
+        <v>0.0008783191442489624</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01364538446068764</v>
+        <v>0.0006106009241193533</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.006375325843691826</v>
+        <v>0.01718162186443806</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01394394133239985</v>
+        <v>0.006705939769744873</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.003387378994375467</v>
+        <v>0.0522664450109005</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001469827257096767</v>
+        <v>0.02714597433805466</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.02155507355928421</v>
+        <v>0.01599367149174213</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.01296724565327168</v>
+        <v>0.001348202116787434</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001101999878301285</v>
+        <v>0.01909425854682922</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7.186830043792725e-05</v>
+        <v>0.01854409649968147</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002481010043993592</v>
+        <v>0.05407581850886345</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0002437015791656449</v>
+        <v>0.005554140079766512</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001217464217916131</v>
+        <v>0.05663799121975899</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0006086996290832758</v>
+        <v>0.01133001875132322</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000397117662942037</v>
+        <v>0.03349849209189415</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002081471320707351</v>
+        <v>0.02443218603730202</v>
       </c>
       <c r="H14" t="n">
-        <v>8.485892612952739e-05</v>
+        <v>0.02469381503760815</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001154811689048074</v>
+        <v>0.004877601284533739</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000154979556100443</v>
+        <v>0.006202842574566603</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00184846471529454</v>
+        <v>0.061114352196455</v>
       </c>
       <c r="L14" t="n">
-        <v>2.100211349898018e-05</v>
+        <v>0.01228211168199778</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0009916622657328844</v>
+        <v>0.0724879652261734</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0006590236444026232</v>
+        <v>0.03186941519379616</v>
       </c>
       <c r="O14" t="n">
-        <v>0.000405360187869519</v>
+        <v>0.03830209001898766</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001804762578103691</v>
+        <v>0.01545164361596107</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0004517233173828572</v>
+        <v>0.002535288222134113</v>
       </c>
       <c r="R14" t="n">
-        <v>3.629446655395441e-05</v>
+        <v>0.001725696725770831</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001235109230037779</v>
+        <v>0.005406396463513374</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0003590112901292741</v>
+        <v>0.004284861497581005</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001279896241612732</v>
+        <v>0.005907689221203327</v>
       </c>
       <c r="V14" t="n">
-        <v>0.000335317658027634</v>
+        <v>0.00435493141412735</v>
       </c>
       <c r="W14" t="n">
-        <v>0.000254015700193122</v>
+        <v>0.01317134033888578</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000232056831009686</v>
+        <v>0.01298538129776716</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001877755421446636</v>
+        <v>0.01320396736264229</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.00030669872649014</v>
+        <v>0.01621461473405361</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001674376835580915</v>
+        <v>0.001401957822963595</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.940906026400626e-05</v>
+        <v>0.003215755801647902</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.763539881329052e-06</v>
+        <v>0.001192220486700535</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001985357521334663</v>
+        <v>0.005404005758464336</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.10049433412496e-05</v>
+        <v>0.02632480300962925</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.224550891900435e-05</v>
+        <v>0.008919232524931431</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.933133848477155e-05</v>
+        <v>0.02425418980419636</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.886650534288492e-05</v>
+        <v>0.001883279765024781</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0002561740693636239</v>
+        <v>0.02904649637639523</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6.442561425501481e-05</v>
+        <v>0.006624942179769278</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.000295779318548739</v>
+        <v>0.001412245444953442</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001253417867701501</v>
+        <v>0.01241029426455498</v>
       </c>
       <c r="AM14" t="n">
-        <v>6.855349511170061e-06</v>
+        <v>0.007984132505953312</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0002205092459917068</v>
+        <v>0.01975125446915627</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0002692256821319461</v>
+        <v>0.00188740249723196</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0002957182296086103</v>
+        <v>0.01178086921572685</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0001088646895368584</v>
+        <v>0.001210779417306185</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0002268785901833326</v>
+        <v>0.005202123895287514</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001287666236748919</v>
+        <v>0.002764279255643487</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.425470302114263e-05</v>
+        <v>0.007244506385177374</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001529453322291374</v>
+        <v>0.04570905491709709</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.280888581182808e-05</v>
+        <v>0.01592900790274143</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.000169945924426429</v>
+        <v>0.01315151061862707</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.299908192071598e-05</v>
+        <v>0.04237444326281548</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.113734707469121e-05</v>
+        <v>0.02479890175163746</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0001794114359654486</v>
+        <v>0.0005194186232984066</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.000347068184055388</v>
+        <v>0.008611040189862251</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.150759872980416e-06</v>
+        <v>0.007878939621150494</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.081166015472263e-05</v>
+        <v>0.002249551005661488</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0003862145822495222</v>
+        <v>0.01403843984007835</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0005343317752704024</v>
+        <v>0.005424781236797571</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0003622743533924222</v>
+        <v>0.01365700643509626</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0008368472335860133</v>
+        <v>0.03765019029378891</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0001965823030332103</v>
+        <v>0.0007463808869943023</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.561243491072673e-05</v>
+        <v>0.00119063863530755</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0003853073867503554</v>
+        <v>0.02635105513036251</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.447872146964073e-05</v>
+        <v>0.00347613194026053</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0002253632701467723</v>
+        <v>0.007801682688295841</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0005001314566470683</v>
+        <v>0.01646699197590351</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0001921637303894386</v>
+        <v>0.0001213403302244842</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.615158493630588e-05</v>
+        <v>0.01554057840257883</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0003008687635883689</v>
+        <v>0.02132316306233406</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0002281210327055305</v>
+        <v>0.008367616683244705</v>
       </c>
       <c r="BR14" t="n">
-        <v>6.128691165940836e-05</v>
+        <v>0.005022399593144655</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0001289154897676781</v>
+        <v>0.009027224034070969</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.300761015154421e-05</v>
+        <v>0.007399147376418114</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001355862332275137</v>
+        <v>0.0006326843285933137</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0008500214898958802</v>
+        <v>0.03064887598156929</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0002427196741336957</v>
+        <v>0.005983420182019472</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0001153073681052774</v>
+        <v>0.01810554228723049</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.009389507089509e-05</v>
+        <v>0.008504676632583141</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0003164646914228797</v>
+        <v>0.02029536664485931</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002399394870735705</v>
+        <v>0.01585251837968826</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.049740477465093e-05</v>
+        <v>0.0005424567498266697</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.265139407129027e-05</v>
+        <v>0.002440566662698984</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.47861444222508e-05</v>
+        <v>0.005145180970430374</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0004027122631669044</v>
+        <v>0.01562757231295109</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001499673089710996</v>
+        <v>0.0005551853682845831</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0001773824624251574</v>
+        <v>0.01703992486000061</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001030880666803569</v>
+        <v>0.006660176906734705</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001034447268466465</v>
+        <v>0.006643951404839754</v>
       </c>
       <c r="CJ14" t="n">
-        <v>8.63411114551127e-05</v>
+        <v>0.002942505525425076</v>
       </c>
       <c r="CK14" t="n">
-        <v>6.497497815871611e-05</v>
+        <v>0.003204440232366323</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0001166548172477633</v>
+        <v>0.001562613761052489</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0004504342505242676</v>
+        <v>0.02204910665750504</v>
       </c>
       <c r="CN14" t="n">
-        <v>5.54505386389792e-05</v>
+        <v>0.03189157694578171</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0001525196566944942</v>
+        <v>0.01730479672551155</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0002524934243410826</v>
+        <v>0.02066355757415295</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0002101718855556101</v>
+        <v>0.01171458885073662</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0005194675177335739</v>
+        <v>0.0001777308061718941</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0002849406737368554</v>
+        <v>0.01422754302620888</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.000213114355574362</v>
+        <v>0.007780314423143864</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0002288326213601977</v>
+        <v>0.003347253194078803</v>
       </c>
       <c r="CV14" t="n">
-        <v>8.39889526105253e-06</v>
+        <v>0.003422314068302512</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0003623165539465845</v>
+        <v>0.01423658803105354</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.000178887537913397</v>
+        <v>0.001824609469622374</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0002549429482314736</v>
+        <v>0.02040418423712254</v>
       </c>
       <c r="CZ14" t="n">
-        <v>9.024923929246143e-05</v>
+        <v>0.01029191166162491</v>
       </c>
       <c r="DA14" t="n">
-        <v>8.961529238149524e-05</v>
+        <v>0.005885595455765724</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001063620584318414</v>
+        <v>0.00386049528606236</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.000130934568005614</v>
+        <v>0.005358191672712564</v>
       </c>
       <c r="DD14" t="n">
-        <v>7.08260340616107e-05</v>
+        <v>0.002713243942707777</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001152786499005742</v>
+        <v>0.008405186235904694</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0006948456866666675</v>
+        <v>0.006380193866789341</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.000205543648917228</v>
+        <v>0.008779183030128479</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0007546317065134645</v>
+        <v>0.01858722791075706</v>
       </c>
       <c r="DI14" t="n">
-        <v>9.563310413795989e-06</v>
+        <v>0.002862523077055812</v>
       </c>
       <c r="DJ14" t="n">
-        <v>8.854025509208441e-05</v>
+        <v>0.01094350405037403</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0001438938779756427</v>
+        <v>0.0004905775422230363</v>
       </c>
       <c r="DL14" t="n">
-        <v>6.887003837618977e-05</v>
+        <v>0.02963021211326122</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0001130578457377851</v>
+        <v>0.006863568909466267</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0002596263366285712</v>
+        <v>0.003167513757944107</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001665833260631189</v>
+        <v>0.01856875419616699</v>
       </c>
       <c r="DP14" t="n">
-        <v>4.184233694104478e-05</v>
+        <v>0.002304580761119723</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.655239460291341e-05</v>
+        <v>0.01368100848048925</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.490984328091145e-05</v>
+        <v>0.009107045829296112</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0001471775758545846</v>
+        <v>0.007656971458345652</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0001344443298876286</v>
+        <v>0.01871959120035172</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001251649082405493</v>
+        <v>0.01265467330813408</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0001203196152346209</v>
+        <v>0.01088174339383841</v>
       </c>
       <c r="DW14" t="n">
-        <v>2.552799742261413e-06</v>
+        <v>0.005029844120144844</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0001600225223228335</v>
+        <v>0.003752843011170626</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002053782081929967</v>
+        <v>0.01016832329332829</v>
       </c>
       <c r="DZ14" t="n">
-        <v>9.526270878268406e-05</v>
+        <v>0.007019658572971821</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0002697698073461652</v>
+        <v>0.02156908996403217</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.08703349926509e-05</v>
+        <v>0.005254771560430527</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0001699290587566793</v>
+        <v>0.005540854297578335</v>
       </c>
       <c r="ED14" t="n">
-        <v>7.855660805944353e-05</v>
+        <v>0.03342365846037865</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0002228770172223449</v>
+        <v>0.01919901929795742</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.000280308595392853</v>
+        <v>0.003515517804771662</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0003867956984322518</v>
+        <v>0.0002958087716251612</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0002132609079126269</v>
+        <v>0.006131354253739119</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0001339002483291551</v>
+        <v>0.007784464862197638</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.000103991333162412</v>
+        <v>0.01325763110071421</v>
       </c>
       <c r="EK14" t="n">
-        <v>8.392406743951142e-05</v>
+        <v>0.006397212855517864</v>
       </c>
       <c r="EL14" t="n">
-        <v>9.933138790074736e-05</v>
+        <v>0.004956360906362534</v>
       </c>
       <c r="EM14" t="n">
-        <v>6.726442370563745e-05</v>
+        <v>0.003096774220466614</v>
       </c>
       <c r="EN14" t="n">
-        <v>5.153051824891008e-05</v>
+        <v>0.00382149894721806</v>
       </c>
       <c r="EO14" t="n">
-        <v>4.826007352676243e-05</v>
+        <v>0.003330677282065153</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0001673225779086351</v>
+        <v>0.0110673401504755</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001710941578494385</v>
+        <v>0.0015299660153687</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001577964139869437</v>
+        <v>0.009579304605722427</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0001050617865985259</v>
+        <v>0.01505319215357304</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0001467749825678766</v>
+        <v>0.002258045366033912</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0002479362883605063</v>
+        <v>0.009312823414802551</v>
       </c>
       <c r="EV14" t="n">
-        <v>4.835941581404768e-05</v>
+        <v>0.00193797901738435</v>
       </c>
       <c r="EW14" t="n">
-        <v>8.741155033931136e-05</v>
+        <v>0.01058682985603809</v>
       </c>
       <c r="EX14" t="n">
-        <v>5.622821481665596e-05</v>
+        <v>0.003363383933901787</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0003713404003065079</v>
+        <v>0.01680031046271324</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0001525192783446983</v>
+        <v>0.0002070605987682939</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0002068110479740426</v>
+        <v>0.02113361284136772</v>
       </c>
       <c r="FB14" t="n">
-        <v>4.162540790275671e-05</v>
+        <v>0.005691771395504475</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0001076703265425749</v>
+        <v>0.007369970437139273</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.000129389125504531</v>
+        <v>0.001121596549637616</v>
       </c>
       <c r="FE14" t="n">
-        <v>8.451172470813617e-05</v>
+        <v>0.006038744002580643</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001338661822956055</v>
+        <v>0.001172131858766079</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001571277098264545</v>
+        <v>0.005066069774329662</v>
       </c>
       <c r="FH14" t="n">
-        <v>9.030581713886932e-05</v>
+        <v>0.002807752229273319</v>
       </c>
       <c r="FI14" t="n">
-        <v>8.376884943572804e-05</v>
+        <v>0.01029188092797995</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0002446958387736231</v>
+        <v>0.01458049286156893</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0002680802426766604</v>
+        <v>0.0009578637545928359</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0002201407478423789</v>
+        <v>0.007437767460942268</v>
       </c>
       <c r="FM14" t="n">
-        <v>9.737888467498124e-05</v>
+        <v>0.006036301143467426</v>
       </c>
       <c r="FN14" t="n">
-        <v>8.055307989707217e-05</v>
+        <v>0.006303400732576847</v>
       </c>
       <c r="FO14" t="n">
-        <v>3.983333954238333e-05</v>
+        <v>0.014606898650527</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001667289761826396</v>
+        <v>0.02232704311609268</v>
       </c>
       <c r="FQ14" t="n">
-        <v>3.056040077353828e-05</v>
+        <v>0.006891144439578056</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0005453897756524384</v>
+        <v>0.021726468577981</v>
       </c>
       <c r="FS14" t="n">
-        <v>3.019539144588634e-05</v>
+        <v>0.0007201423868536949</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0002942952851299196</v>
+        <v>0.009273254312574863</v>
       </c>
       <c r="FU14" t="n">
-        <v>6.864154420327395e-05</v>
+        <v>0.0007464115624316037</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001129079755628482</v>
+        <v>0.01657210104167461</v>
       </c>
       <c r="FW14" t="n">
-        <v>7.167589501477778e-05</v>
+        <v>0.01046837959438562</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002818943466991186</v>
+        <v>0.004084557760506868</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0002951411297544837</v>
+        <v>0.003341217059642076</v>
       </c>
       <c r="FZ14" t="n">
-        <v>5.616593261947855e-05</v>
+        <v>0.0015416971873492</v>
       </c>
       <c r="GA14" t="n">
-        <v>4.459324918570928e-05</v>
+        <v>0.009555811993777752</v>
       </c>
       <c r="GB14" t="n">
-        <v>3.466659836703911e-05</v>
+        <v>0.009618427604436874</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0001251421490451321</v>
+        <v>0.003711653407663107</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.000237721498706378</v>
+        <v>0.01314697042107582</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0004431411798577756</v>
+        <v>0.02734378539025784</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001861512137111276</v>
+        <v>0.00079702417133376</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0002503120340406895</v>
+        <v>0.002761267824098468</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.634628956206143e-05</v>
+        <v>0.003104299306869507</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002608494367450476</v>
+        <v>0.008840475231409073</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0005199973820708692</v>
+        <v>0.0007830198737792671</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001895896624773741</v>
+        <v>0.01880566962063313</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001134403981268406</v>
+        <v>0.0002612743410281837</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0002978367265313864</v>
+        <v>0.008406883105635643</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0007149247103370726</v>
+        <v>0.008356450125575066</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0003871928784064949</v>
+        <v>0.0088893948122859</v>
       </c>
       <c r="I15" t="n">
-        <v>6.856965774204582e-05</v>
+        <v>0.004125196021050215</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000265271810349077</v>
+        <v>0.004885051399469376</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001932693761773407</v>
+        <v>0.005537260789424181</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002464304561726749</v>
+        <v>0.001066715340130031</v>
       </c>
       <c r="M15" t="n">
-        <v>0.001846997067332268</v>
+        <v>0.0248710922896862</v>
       </c>
       <c r="N15" t="n">
-        <v>0.001355327549390495</v>
+        <v>0.004121233709156513</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0008395555196329951</v>
+        <v>0.008832533843815327</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0005502479034475982</v>
+        <v>0.009265802800655365</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.000104337086668238</v>
+        <v>0.003275275696069002</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0002454334462527186</v>
+        <v>0.003761447034776211</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0001336298591922969</v>
+        <v>0.001521488884463906</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0005662179319187999</v>
+        <v>0.001891175983473659</v>
       </c>
       <c r="U15" t="n">
-        <v>2.925269291154109e-05</v>
+        <v>0.0005107531324028969</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0003562513156794012</v>
+        <v>0.00256233150139451</v>
       </c>
       <c r="W15" t="n">
-        <v>8.496432565152645e-05</v>
+        <v>0.005258307326585054</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0002499350230209529</v>
+        <v>0.003634658409282565</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0003943046031054109</v>
+        <v>0.0002427090657874942</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0002949054178316146</v>
+        <v>0.0009290758171118796</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0003199341590516269</v>
+        <v>0.0008330750279128551</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.268712554126978e-05</v>
+        <v>0.0008259589085355401</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0005825919797644019</v>
+        <v>0.001721547450870275</v>
       </c>
       <c r="AD15" t="n">
-        <v>9.570464317221195e-05</v>
+        <v>0.001854551606811583</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0001337566791335121</v>
+        <v>0.001877699862234294</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.915116783697158e-05</v>
+        <v>0.002404805272817612</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0002452752087265253</v>
+        <v>0.004345801193267107</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0003493879630696028</v>
+        <v>0.002559313783422112</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0002813077881000936</v>
+        <v>0.002963057719171047</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.000109214372059796</v>
+        <v>0.002223289338871837</v>
       </c>
       <c r="AK15" t="n">
-        <v>6.012019730405882e-05</v>
+        <v>0.002124752150848508</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0005505739245563745</v>
+        <v>0.002385894767940044</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.75164605025202e-05</v>
+        <v>0.001219211146235466</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.558578464435413e-05</v>
+        <v>0.00647857366129756</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0001030698476824909</v>
+        <v>0.0008310141274705529</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.0002107392792822793</v>
+        <v>0.004115044139325619</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0003019198775291443</v>
+        <v>0.004013344645500183</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0001489626156399027</v>
+        <v>0.0008810017025098205</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0001382565242238343</v>
+        <v>0.0005777549231424928</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0003035722183994949</v>
+        <v>0.007040563970804214</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.002002831315621734</v>
+        <v>0.008269039914011955</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0001349854865111411</v>
+        <v>0.003520123893395066</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.000554863247089088</v>
+        <v>0.006424728315323591</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0004117642238270491</v>
+        <v>0.008350730873644352</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.968117223645095e-05</v>
+        <v>0.004852864891290665</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0002820775262080133</v>
+        <v>0.002203140873461962</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.611301483237185e-05</v>
+        <v>4.457542672753334e-07</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.170990748913027e-05</v>
+        <v>0.003722338704392314</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.119790249504149e-05</v>
+        <v>0.00159176648594439</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0002532155194785446</v>
+        <v>0.0003153829893562943</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0005154047394171357</v>
+        <v>0.001070826547220349</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0006923216860741377</v>
+        <v>0.004312623757869005</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0009626045357435942</v>
+        <v>0.005725994240492582</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0002588712959550321</v>
+        <v>0.0003568489337339997</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0004108736175112426</v>
+        <v>0.0008913481142371893</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0001255953684449196</v>
+        <v>0.004572752863168716</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0002604893525131047</v>
+        <v>0.001206648303195834</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0002230977261206135</v>
+        <v>0.0008063085842877626</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0003228166024200618</v>
+        <v>0.004389808978885412</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0002746355021372437</v>
+        <v>0.003333135042339563</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.827661905437708e-05</v>
+        <v>0.004475947003811598</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0001085417461581528</v>
+        <v>0.004649138078093529</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0003665206022560596</v>
+        <v>0.002713667927309871</v>
       </c>
       <c r="BR15" t="n">
-        <v>2.240887079096865e-05</v>
+        <v>0.001842107623815536</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.486843631137162e-05</v>
+        <v>0.00146772840525955</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0001417645835317671</v>
+        <v>0.001019671675749123</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.0002575903781689703</v>
+        <v>0.003078913548961282</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.001168442657217383</v>
+        <v>0.006982584949582815</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.0005587156629189849</v>
+        <v>0.0006101674516685307</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0004444321675691754</v>
+        <v>0.00676264613866806</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0001440835767425597</v>
+        <v>0.002918723970651627</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0001883415097836405</v>
+        <v>0.006267782300710678</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0002080834965454414</v>
+        <v>0.002565136877819896</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0001295791880693287</v>
+        <v>0.0002301100175827742</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0002281019405927509</v>
+        <v>0.0003077075816690922</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.990689194528386e-05</v>
+        <v>0.0005544635350815952</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0004483958764467388</v>
+        <v>0.0009979507885873318</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0001691402867436409</v>
+        <v>0.001195056247524917</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0002623296168167144</v>
+        <v>0.006670225411653519</v>
       </c>
       <c r="CH15" t="n">
-        <v>6.809288606746122e-05</v>
+        <v>4.637382517103106e-06</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0002250914403703064</v>
+        <v>0.001624624943360686</v>
       </c>
       <c r="CJ15" t="n">
-        <v>6.302641122601926e-05</v>
+        <v>0.0005413144826889038</v>
       </c>
       <c r="CK15" t="n">
-        <v>7.137686770875007e-05</v>
+        <v>0.001570221153087914</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0001335237466264516</v>
+        <v>0.0001949744037119672</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0004693402734119445</v>
+        <v>0.002779272152110934</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0001835917355492711</v>
+        <v>0.002006184076890349</v>
       </c>
       <c r="CO15" t="n">
-        <v>5.281283301883377e-05</v>
+        <v>0.001251151436008513</v>
       </c>
       <c r="CP15" t="n">
-        <v>5.941881681792438e-05</v>
+        <v>0.009491467848420143</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0001242310827365145</v>
+        <v>0.0006051770178601146</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.000268239266006276</v>
+        <v>5.806074477732182e-05</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0003817706601694226</v>
+        <v>0.003832424525171518</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0005023548728786409</v>
+        <v>0.00140076014213264</v>
       </c>
       <c r="CU15" t="n">
-        <v>7.949907740112394e-05</v>
+        <v>0.002748240483924747</v>
       </c>
       <c r="CV15" t="n">
-        <v>3.638752241386101e-05</v>
+        <v>0.0008014370105229318</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0003360213595442474</v>
+        <v>0.0005966497701592743</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.0002119405689882115</v>
+        <v>0.0009860603604465723</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0003094547428190708</v>
+        <v>0.006724958308041096</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.862645098706707e-05</v>
+        <v>0.001514654606580734</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0003304770507384092</v>
+        <v>0.001346516655758023</v>
       </c>
       <c r="DB15" t="n">
-        <v>5.415413397713564e-05</v>
+        <v>0.0001380661851726472</v>
       </c>
       <c r="DC15" t="n">
-        <v>5.904877252760343e-05</v>
+        <v>0.001509679947048426</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.761166251730174e-05</v>
+        <v>0.0007476472528651357</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.000200869602849707</v>
+        <v>0.004589845426380634</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0002900200197473168</v>
+        <v>0.00403711199760437</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.0001608243910595775</v>
+        <v>0.0004499778151512146</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.000709807442035526</v>
+        <v>0.004876920953392982</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0002090376219712198</v>
+        <v>0.0005757466424256563</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0003891498490702361</v>
+        <v>0.00483021792024374</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.0001842447236413136</v>
+        <v>0.002779063303023577</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.0002654551062732935</v>
+        <v>0.007715982384979725</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0002365119435125962</v>
+        <v>0.002637308090925217</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.0001705701579339802</v>
+        <v>0.001765685970894992</v>
       </c>
       <c r="DO15" t="n">
-        <v>9.585206862539053e-05</v>
+        <v>0.002544356044381857</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.0001421109773218632</v>
+        <v>0.001271750777959824</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0001003311626845971</v>
+        <v>0.0002319453051313758</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0001792967523215339</v>
+        <v>0.0005448002484627068</v>
       </c>
       <c r="DS15" t="n">
-        <v>2.03652489290107e-05</v>
+        <v>0.004333606455475092</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.0002717166789807379</v>
+        <v>0.0008886540308594704</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0002396295894868672</v>
+        <v>0.003256978932768106</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.0003149759722873569</v>
+        <v>0.005480568390339613</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0001143056942964904</v>
+        <v>0.001059921807609499</v>
       </c>
       <c r="DX15" t="n">
-        <v>1.15024695332977e-05</v>
+        <v>0.004765899851918221</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.000432567932875827</v>
+        <v>0.003201748244464397</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0003162955981679261</v>
+        <v>0.002583653666079044</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0002695945440791547</v>
+        <v>0.002517646178603172</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.000191182378330268</v>
+        <v>0.0009437104454264045</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.000136750633828342</v>
+        <v>0.0002601150190457702</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0001269933709409088</v>
+        <v>0.006030771415680647</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0001110048542614095</v>
+        <v>0.002082273596897721</v>
       </c>
       <c r="EF15" t="n">
-        <v>5.882511322852224e-05</v>
+        <v>0.001773627242073417</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0003701180103234947</v>
+        <v>0.002585572889074683</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0002208701625932008</v>
+        <v>3.333878703415394e-05</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0003035559784621</v>
+        <v>0.006594025529921055</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0002461847616359591</v>
+        <v>0.0009306402644142509</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0003714339691214263</v>
+        <v>0.001235269708558917</v>
       </c>
       <c r="EL15" t="n">
-        <v>7.190500036813319e-05</v>
+        <v>0.001085549127310514</v>
       </c>
       <c r="EM15" t="n">
-        <v>2.496499473636504e-05</v>
+        <v>0.0005912175984121859</v>
       </c>
       <c r="EN15" t="n">
-        <v>3.751670010387897e-05</v>
+        <v>0.0004143765545450151</v>
       </c>
       <c r="EO15" t="n">
-        <v>2.835361374309286e-05</v>
+        <v>0.002562545938417315</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0002035859070019796</v>
+        <v>0.00276929559186101</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0004338131402619183</v>
+        <v>0.0009313634363934398</v>
       </c>
       <c r="ER15" t="n">
-        <v>8.387409616261721e-05</v>
+        <v>0.007764835841953754</v>
       </c>
       <c r="ES15" t="n">
-        <v>1.297994640481193e-05</v>
+        <v>0.00139236357063055</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0003806943714153022</v>
+        <v>0.00134955917019397</v>
       </c>
       <c r="EU15" t="n">
-        <v>6.077605939935893e-05</v>
+        <v>0.003124513663351536</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.000225348339881748</v>
+        <v>0.0009525443310849369</v>
       </c>
       <c r="EW15" t="n">
-        <v>1.49810039147269e-05</v>
+        <v>0.006220221519470215</v>
       </c>
       <c r="EX15" t="n">
-        <v>4.440909106051549e-05</v>
+        <v>0.0009445033501833677</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0003711025347001851</v>
+        <v>0.00217719841748476</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0001406221563229337</v>
+        <v>0.0005813679890707135</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0003819955454673618</v>
+        <v>0.007286864798516035</v>
       </c>
       <c r="FB15" t="n">
-        <v>4.992288086214103e-05</v>
+        <v>0.0005409537698142231</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0002982441510539502</v>
+        <v>0.002368325367569923</v>
       </c>
       <c r="FD15" t="n">
-        <v>6.313278572633862e-05</v>
+        <v>0.0001317793794441968</v>
       </c>
       <c r="FE15" t="n">
-        <v>5.399917063186876e-05</v>
+        <v>0.001506885513663292</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0001152690383605659</v>
+        <v>0.0001553649490233511</v>
       </c>
       <c r="FG15" t="n">
-        <v>6.004177703289315e-05</v>
+        <v>0.00165340572129935</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0002662054030224681</v>
+        <v>0.0003493158146739006</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.0002995317045133561</v>
+        <v>0.002971663139760494</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0001576596696395427</v>
+        <v>0.001535257208161056</v>
       </c>
       <c r="FK15" t="n">
-        <v>7.031449058558792e-05</v>
+        <v>0.001271461136639118</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0002716209855861962</v>
+        <v>0.001794650917872787</v>
       </c>
       <c r="FM15" t="n">
-        <v>6.044444307917729e-05</v>
+        <v>0.00265758647583425</v>
       </c>
       <c r="FN15" t="n">
-        <v>1.240504752786364e-05</v>
+        <v>0.001895445166155696</v>
       </c>
       <c r="FO15" t="n">
-        <v>3.703223410411738e-05</v>
+        <v>0.0002891041804105043</v>
       </c>
       <c r="FP15" t="n">
-        <v>1.17002782644704e-05</v>
+        <v>0.001927323872223496</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0004552056489046663</v>
+        <v>0.001029514940455556</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0003408289339859039</v>
+        <v>0.00474835280328989</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0006961087929084897</v>
+        <v>0.003064854769036174</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0001688291522441432</v>
+        <v>0.002474074717611074</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0002246964868390933</v>
+        <v>0.000757429632358253</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0001387989323120564</v>
+        <v>0.003187760012224317</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0002906531153712422</v>
+        <v>0.008347571827471256</v>
       </c>
       <c r="FX15" t="n">
-        <v>7.852303679101169e-05</v>
+        <v>0.000362829421646893</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.0004502948140725493</v>
+        <v>0.00200440501794219</v>
       </c>
       <c r="FZ15" t="n">
-        <v>9.33715928113088e-05</v>
+        <v>4.512653686106205e-05</v>
       </c>
       <c r="GA15" t="n">
-        <v>6.175979069666937e-05</v>
+        <v>0.00423073023557663</v>
       </c>
       <c r="GB15" t="n">
-        <v>3.093508712481707e-05</v>
+        <v>0.003491229843348265</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.641143899178132e-05</v>
+        <v>0.003400483634322882</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0002238446177216247</v>
+        <v>0.007068488281220198</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.001025233301334083</v>
+        <v>0.003288880456238985</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0001683114096522331</v>
+        <v>0.001632843632251024</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0002537359250709414</v>
+        <v>0.002695453586056828</v>
       </c>
     </row>
   </sheetData>
